--- a/listings.xlsx
+++ b/listings.xlsx
@@ -53,24 +53,30 @@
     <t>PARIS 7ÈME</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87108484.html</t>
+  </si>
+  <si>
+    <t>PARIS 16ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87141456.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87146307.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87135906.html</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87108484.html</t>
-  </si>
-  <si>
-    <t>PARIS 16ÈME</t>
-  </si>
-  <si>
-    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87141456.html</t>
-  </si>
-  <si>
-    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87146307.html</t>
-  </si>
-  <si>
-    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87135906.html</t>
-  </si>
-  <si>
     <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87108483.html</t>
   </si>
   <si>
@@ -410,12 +416,6 @@
     <t>Paris 15ème</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/273206899.htm</t>
   </si>
   <si>
@@ -452,10 +452,10 @@
     <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639859.htm</t>
   </si>
   <si>
-    <t>1 / 14</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/274285499.htm</t>
+    <t>1 / 15</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/montreuil-93/ruffins-theophile-sueur-montreau-le-morillon/270926483.htm</t>
   </si>
   <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639863.htm</t>
@@ -512,10 +512,10 @@
     <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/cambronne-garibaldi/274316193.htm</t>
   </si>
   <si>
-    <t>Nouveau</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/saint-ouen-93/marie-godillot-landy/273787275.htm</t>
+    <t>1 941 € /mois</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/issy-les-moulineaux-92/273103027.htm</t>
   </si>
   <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273630989.htm</t>
@@ -548,7 +548,7 @@
     <t>Prospector — Paris Listings</t>
   </si>
   <si>
-    <t>Generated: 07/07/2026, 14:13:39</t>
+    <t>Generated: 07/07/2026, 14:37:55</t>
   </si>
   <si>
     <t>Barnes: 100 listings</t>
@@ -1042,13 +1042,13 @@
         <v>13</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1071,7 +1071,7 @@
         <f>B3/E3</f>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>13</v>
@@ -1083,7 +1083,7 @@
         <v>13</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1106,19 +1106,19 @@
         <f>B4/E4</f>
       </c>
       <c r="G4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1147,13 +1147,13 @@
         <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1179,16 +1179,16 @@
         <v>12</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1211,19 +1211,19 @@
         <f>B7/E7</f>
       </c>
       <c r="G7" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1246,7 +1246,7 @@
         <f>B8/E8</f>
       </c>
       <c r="G8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>13</v>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1281,7 +1281,7 @@
         <f>B9/E9</f>
       </c>
       <c r="G9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>13</v>
@@ -1290,10 +1290,10 @@
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1322,13 +1322,13 @@
         <v>13</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1349,19 +1349,19 @@
         <f>B11/E11</f>
       </c>
       <c r="G11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1382,19 +1382,19 @@
         <f>B12/E12</f>
       </c>
       <c r="G12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1417,19 +1417,19 @@
         <f>B13/E13</f>
       </c>
       <c r="G13" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1452,19 +1452,19 @@
         <f>B14/E14</f>
       </c>
       <c r="G14" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1487,7 +1487,7 @@
         <f>B15/E15</f>
       </c>
       <c r="G15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>13</v>
@@ -1499,7 +1499,7 @@
         <v>13</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1518,19 +1518,19 @@
         <f>B16/E16</f>
       </c>
       <c r="G16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1553,19 +1553,19 @@
         <f>B17/E17</f>
       </c>
       <c r="G17" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1588,19 +1588,19 @@
         <f>B18/E18</f>
       </c>
       <c r="G18" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1619,19 +1619,19 @@
         <f>B19/E19</f>
       </c>
       <c r="G19" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1654,19 +1654,19 @@
         <f>B20/E20</f>
       </c>
       <c r="G20" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1689,19 +1689,19 @@
         <f>B21/E21</f>
       </c>
       <c r="G21" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1724,19 +1724,19 @@
         <f>B22/E22</f>
       </c>
       <c r="G22" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1759,19 +1759,19 @@
         <f>B23/E23</f>
       </c>
       <c r="G23" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1794,19 +1794,19 @@
         <f>B24/E24</f>
       </c>
       <c r="G24" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1829,19 +1829,19 @@
         <f>B25/E25</f>
       </c>
       <c r="G25" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1864,19 +1864,19 @@
         <f>B26/E26</f>
       </c>
       <c r="G26" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1899,19 +1899,19 @@
         <f>B27/E27</f>
       </c>
       <c r="G27" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1934,7 +1934,7 @@
         <f>B28/E28</f>
       </c>
       <c r="G28" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>13</v>
@@ -1946,7 +1946,7 @@
         <v>13</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1975,13 +1975,13 @@
         <v>13</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2004,7 +2004,7 @@
         <f>B30/E30</f>
       </c>
       <c r="G30" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>13</v>
@@ -2013,10 +2013,10 @@
         <v>13</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2039,7 +2039,7 @@
         <f>B31/E31</f>
       </c>
       <c r="G31" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>13</v>
@@ -2051,7 +2051,7 @@
         <v>13</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2083,10 +2083,10 @@
         <v>13</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2112,16 +2112,16 @@
         <v>12</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2144,19 +2144,19 @@
         <f>B34/E34</f>
       </c>
       <c r="G34" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2177,19 +2177,19 @@
         <f>B35/E35</f>
       </c>
       <c r="G35" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2212,19 +2212,19 @@
         <f>B36/E36</f>
       </c>
       <c r="G36" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2250,16 +2250,16 @@
         <v>12</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2291,10 +2291,10 @@
         <v>13</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2317,19 +2317,19 @@
         <f>B39/E39</f>
       </c>
       <c r="G39" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2358,13 +2358,13 @@
         <v>13</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2387,19 +2387,19 @@
         <f>B41/E41</f>
       </c>
       <c r="G41" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2428,13 +2428,13 @@
         <v>13</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2469,7 +2469,7 @@
         <v>13</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2498,13 +2498,13 @@
         <v>13</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2527,19 +2527,19 @@
         <f>B45/E45</f>
       </c>
       <c r="G45" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2562,19 +2562,19 @@
         <f>B46/E46</f>
       </c>
       <c r="G46" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2597,19 +2597,19 @@
         <f>B47/E47</f>
       </c>
       <c r="G47" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2632,7 +2632,7 @@
         <f>B48/E48</f>
       </c>
       <c r="G48" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>13</v>
@@ -2644,7 +2644,7 @@
         <v>13</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2676,10 +2676,10 @@
         <v>13</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2702,19 +2702,19 @@
         <f>B50/E50</f>
       </c>
       <c r="G50" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2737,7 +2737,7 @@
         <f>B51/E51</f>
       </c>
       <c r="G51" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>13</v>
@@ -2749,7 +2749,7 @@
         <v>13</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2772,7 +2772,7 @@
         <f>B52/E52</f>
       </c>
       <c r="G52" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>13</v>
@@ -2784,7 +2784,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2807,7 +2807,7 @@
         <f>B53/E53</f>
       </c>
       <c r="G53" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>13</v>
@@ -2816,10 +2816,10 @@
         <v>13</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2842,19 +2842,19 @@
         <f>B54/E54</f>
       </c>
       <c r="G54" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2877,19 +2877,19 @@
         <f>B55/E55</f>
       </c>
       <c r="G55" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2912,7 +2912,7 @@
         <f>B56/E56</f>
       </c>
       <c r="G56" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>13</v>
@@ -2924,7 +2924,7 @@
         <v>13</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2947,19 +2947,19 @@
         <f>B57/E57</f>
       </c>
       <c r="G57" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2982,19 +2982,19 @@
         <f>B58/E58</f>
       </c>
       <c r="G58" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3017,19 +3017,19 @@
         <f>B59/E59</f>
       </c>
       <c r="G59" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3058,13 +3058,13 @@
         <v>13</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3099,7 +3099,7 @@
         <v>13</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3122,7 +3122,7 @@
         <f>B62/E62</f>
       </c>
       <c r="G62" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>13</v>
@@ -3131,10 +3131,10 @@
         <v>13</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3157,19 +3157,19 @@
         <f>B63/E63</f>
       </c>
       <c r="G63" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3192,7 +3192,7 @@
         <f>B64/E64</f>
       </c>
       <c r="G64" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>13</v>
@@ -3201,10 +3201,10 @@
         <v>13</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3227,19 +3227,19 @@
         <f>B65/E65</f>
       </c>
       <c r="G65" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3262,19 +3262,19 @@
         <f>B66/E66</f>
       </c>
       <c r="G66" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3300,16 +3300,16 @@
         <v>12</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3332,19 +3332,19 @@
         <f>B68/E68</f>
       </c>
       <c r="G68" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3367,19 +3367,19 @@
         <f>B69/E69</f>
       </c>
       <c r="G69" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3402,19 +3402,19 @@
         <f>B70/E70</f>
       </c>
       <c r="G70" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3437,7 +3437,7 @@
         <f>B71/E71</f>
       </c>
       <c r="G71" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>13</v>
@@ -3449,7 +3449,7 @@
         <v>13</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3472,19 +3472,19 @@
         <f>B72/E72</f>
       </c>
       <c r="G72" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3507,7 +3507,7 @@
         <f>B73/E73</f>
       </c>
       <c r="G73" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>13</v>
@@ -3516,10 +3516,10 @@
         <v>13</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3542,19 +3542,19 @@
         <f>B74/E74</f>
       </c>
       <c r="G74" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3577,7 +3577,7 @@
         <f>B75/E75</f>
       </c>
       <c r="G75" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>13</v>
@@ -3589,7 +3589,7 @@
         <v>13</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3612,19 +3612,19 @@
         <f>B76/E76</f>
       </c>
       <c r="G76" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3643,19 +3643,19 @@
         <f>B77/E77</f>
       </c>
       <c r="G77" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J77" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3684,13 +3684,13 @@
         <v>13</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3719,13 +3719,13 @@
         <v>13</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J79" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3748,19 +3748,19 @@
         <f>B80/E80</f>
       </c>
       <c r="G80" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J80" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3783,19 +3783,19 @@
         <f>B81/E81</f>
       </c>
       <c r="G81" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3818,7 +3818,7 @@
         <f>B82/E82</f>
       </c>
       <c r="G82" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>13</v>
@@ -3830,7 +3830,7 @@
         <v>13</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3853,19 +3853,19 @@
         <f>B83/E83</f>
       </c>
       <c r="G83" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3900,7 +3900,7 @@
         <v>13</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3923,19 +3923,19 @@
         <f>B85/E85</f>
       </c>
       <c r="G85" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3958,19 +3958,19 @@
         <f>B86/E86</f>
       </c>
       <c r="G86" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3993,19 +3993,19 @@
         <f>B87/E87</f>
       </c>
       <c r="G87" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4028,7 +4028,7 @@
         <f>B88/E88</f>
       </c>
       <c r="G88" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>13</v>
@@ -4037,10 +4037,10 @@
         <v>13</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4063,7 +4063,7 @@
         <f>B89/E89</f>
       </c>
       <c r="G89" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>13</v>
@@ -4075,7 +4075,7 @@
         <v>13</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4098,19 +4098,19 @@
         <f>B90/E90</f>
       </c>
       <c r="G90" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4133,7 +4133,7 @@
         <f>B91/E91</f>
       </c>
       <c r="G91" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>13</v>
@@ -4145,7 +4145,7 @@
         <v>13</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4168,19 +4168,19 @@
         <f>B92/E92</f>
       </c>
       <c r="G92" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4203,19 +4203,19 @@
         <f>B93/E93</f>
       </c>
       <c r="G93" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J93" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4238,19 +4238,19 @@
         <f>B94/E94</f>
       </c>
       <c r="G94" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4273,7 +4273,7 @@
         <f>B95/E95</f>
       </c>
       <c r="G95" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>13</v>
@@ -4285,7 +4285,7 @@
         <v>13</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4308,7 +4308,7 @@
         <f>B96/E96</f>
       </c>
       <c r="G96" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>13</v>
@@ -4320,7 +4320,7 @@
         <v>13</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4343,19 +4343,19 @@
         <f>B97/E97</f>
       </c>
       <c r="G97" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4378,19 +4378,19 @@
         <f>B98/E98</f>
       </c>
       <c r="G98" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="99" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4419,13 +4419,13 @@
         <v>13</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="100" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4451,16 +4451,16 @@
         <v>12</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4483,24 +4483,24 @@
         <f>B101/E101</f>
       </c>
       <c r="G101" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B102" s="4">
         <v>2200</v>
@@ -4518,16 +4518,16 @@
         <f>B102/E102</f>
       </c>
       <c r="G102" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>134</v>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="103" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B103" s="4">
         <v>7900</v>
@@ -4556,13 +4556,13 @@
         <v>135</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>136</v>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="104" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B104" s="4">
         <v>6330</v>
@@ -4591,13 +4591,13 @@
         <v>137</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>138</v>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="105" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B105" s="4">
         <v>4700</v>
@@ -4623,16 +4623,16 @@
         <f>B105/E105</f>
       </c>
       <c r="G105" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>139</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="106" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B106" s="4">
         <v>2700</v>
@@ -4658,16 +4658,16 @@
         <f>B106/E106</f>
       </c>
       <c r="G106" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K106" s="3" t="s">
         <v>140</v>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="107" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B107" s="4">
         <v>2250</v>
@@ -4693,16 +4693,16 @@
         <f>B107/E107</f>
       </c>
       <c r="G107" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>141</v>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="108" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B108" s="4">
         <v>4150</v>
@@ -4731,13 +4731,13 @@
         <v>142</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>143</v>
@@ -4745,7 +4745,7 @@
     </row>
     <row r="109" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B109" s="4">
         <v>1890</v>
@@ -4763,16 +4763,16 @@
         <f>B109/E109</f>
       </c>
       <c r="G109" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>144</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="110" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B110" s="4">
         <v>1100</v>
@@ -4801,13 +4801,13 @@
         <v>142</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>145</v>
@@ -4815,19 +4815,19 @@
     </row>
     <row r="111" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B111" s="4">
-        <v>1350</v>
+        <v>1525</v>
       </c>
       <c r="C111" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" s="3">
         <v>1</v>
       </c>
       <c r="E111" s="3">
-        <v>46</v>
+        <v>66.1</v>
       </c>
       <c r="F111" s="5">
         <f>B111/E111</f>
@@ -4836,13 +4836,13 @@
         <v>146</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K111" s="3" t="s">
         <v>147</v>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="112" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B112" s="4">
         <v>1100</v>
@@ -4871,13 +4871,13 @@
         <v>142</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>148</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="113" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B113" s="4">
         <v>2100</v>
@@ -4906,13 +4906,13 @@
         <v>149</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K113" s="3" t="s">
         <v>150</v>
@@ -4920,7 +4920,7 @@
     </row>
     <row r="114" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B114" s="4">
         <v>1603</v>
@@ -4941,13 +4941,13 @@
         <v>151</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K114" s="3" t="s">
         <v>152</v>
@@ -4955,7 +4955,7 @@
     </row>
     <row r="115" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B115" s="4">
         <v>2200</v>
@@ -4976,13 +4976,13 @@
         <v>135</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K115" s="3" t="s">
         <v>153</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="116" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B116" s="4">
         <v>162190</v>
@@ -5011,13 +5011,13 @@
         <v>154</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K116" s="3" t="s">
         <v>155</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="117" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B117" s="4">
         <v>3650</v>
@@ -5046,13 +5046,13 @@
         <v>149</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K117" s="3" t="s">
         <v>156</v>
@@ -5060,7 +5060,7 @@
     </row>
     <row r="118" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B118" s="4">
         <v>7250</v>
@@ -5081,13 +5081,13 @@
         <v>157</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K118" s="3" t="s">
         <v>158</v>
@@ -5095,7 +5095,7 @@
     </row>
     <row r="119" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B119" s="4">
         <v>1500</v>
@@ -5116,13 +5116,13 @@
         <v>159</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K119" s="3" t="s">
         <v>160</v>
@@ -5130,7 +5130,7 @@
     </row>
     <row r="120" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B120" s="4">
         <v>8900</v>
@@ -5151,13 +5151,13 @@
         <v>161</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K120" s="3" t="s">
         <v>162</v>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="121" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B121" s="4">
         <v>1100</v>
@@ -5183,16 +5183,16 @@
         <f>B121/E121</f>
       </c>
       <c r="G121" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K121" s="3" t="s">
         <v>163</v>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="122" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B122" s="4">
         <v>2850</v>
@@ -5221,13 +5221,13 @@
         <v>135</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K122" s="3" t="s">
         <v>164</v>
@@ -5235,7 +5235,7 @@
     </row>
     <row r="123" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B123" s="4">
         <v>2985</v>
@@ -5253,16 +5253,16 @@
         <f>B123/E123</f>
       </c>
       <c r="G123" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K123" s="3" t="s">
         <v>165</v>
@@ -5270,19 +5270,19 @@
     </row>
     <row r="124" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B124" s="4">
-        <v>680</v>
+        <v>1941</v>
       </c>
       <c r="C124" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D124" s="3">
         <v>1</v>
       </c>
       <c r="E124" s="3">
-        <v>22</v>
+        <v>65.1</v>
       </c>
       <c r="F124" s="5">
         <f>B124/E124</f>
@@ -5291,13 +5291,13 @@
         <v>166</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K124" s="3" t="s">
         <v>167</v>
@@ -5305,7 +5305,7 @@
     </row>
     <row r="125" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B125" s="4">
         <v>1200</v>
@@ -5326,13 +5326,13 @@
         <v>142</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K125" s="3" t="s">
         <v>168</v>
@@ -5340,7 +5340,7 @@
     </row>
     <row r="126" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B126" s="4">
         <v>1200</v>
@@ -5358,16 +5358,16 @@
         <f>B126/E126</f>
       </c>
       <c r="G126" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K126" s="3" t="s">
         <v>169</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="127" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B127" s="4">
         <v>1850</v>
@@ -5393,16 +5393,16 @@
         <f>B127/E127</f>
       </c>
       <c r="G127" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>170</v>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="128" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B128" s="4">
         <v>1420</v>
@@ -5428,16 +5428,16 @@
         <f>B128/E128</f>
       </c>
       <c r="G128" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K128" s="3" t="s">
         <v>171</v>
@@ -5445,7 +5445,7 @@
     </row>
     <row r="129" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B129" s="4">
         <v>1175</v>
@@ -5466,13 +5466,13 @@
         <v>149</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K129" s="3" t="s">
         <v>172</v>
@@ -5480,7 +5480,7 @@
     </row>
     <row r="130" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B130" s="4">
         <v>1255</v>
@@ -5501,13 +5501,13 @@
         <v>142</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K130" s="3" t="s">
         <v>173</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="131" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B131" s="4">
         <v>4500</v>
@@ -5536,13 +5536,13 @@
         <v>174</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="K131" s="3" t="s">
         <v>175</v>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="132" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B132" s="4">
         <v>2095</v>
@@ -5568,16 +5568,16 @@
         <f>B132/E132</f>
       </c>
       <c r="G132" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="K132" s="3" t="s">
         <v>176</v>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="179">
   <si>
     <t>Source</t>
   </si>
@@ -251,6 +251,9 @@
     <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-2766079.html</t>
   </si>
   <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-2eme/ref-APM-2765566.html</t>
+  </si>
+  <si>
     <t>https://www.barnes-international.com/en/for-rent/france/paris-17eme/ref-APM-7468343.html</t>
   </si>
   <si>
@@ -404,12 +407,6 @@
     <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87067410.html</t>
   </si>
   <si>
-    <t>PARIS 11ÈME</t>
-  </si>
-  <si>
-    <t>https://www.barnes-international.com/en/for-rent/france/paris-11eme/ref-APM-86050237.html</t>
-  </si>
-  <si>
     <t>SeLoger</t>
   </si>
   <si>
@@ -425,46 +422,49 @@
     <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273678077.htm</t>
   </si>
   <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273866199.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/violet-commerce/273849353.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/272541147.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273864065.htm</t>
+  </si>
+  <si>
+    <t>Paris 16ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639859.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273302365.htm</t>
+  </si>
+  <si>
+    <t>1 220 € /mois</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/suresnes-92/carnot-gambetta/262906241.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639863.htm</t>
+  </si>
+  <si>
+    <t>Paris 18ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273307251.htm</t>
+  </si>
+  <si>
     <t>Paris 6ème</t>
   </si>
   <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/rennes/272330823.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273866199.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/violet-commerce/273849353.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/272541147.htm</t>
-  </si>
-  <si>
-    <t>Paris 16ème</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273302365.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273864065.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639859.htm</t>
-  </si>
-  <si>
-    <t>1 / 15</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/montreuil-93/ruffins-theophile-sueur-montreau-le-morillon/270926483.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639863.htm</t>
-  </si>
-  <si>
-    <t>Paris 18ème</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273307251.htm</t>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274270579.htm</t>
   </si>
   <si>
     <t>Paris 19ème</t>
@@ -473,9 +473,6 @@
     <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273923913.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274270579.htm</t>
-  </si>
-  <si>
     <t>Paris 7ème</t>
   </si>
   <si>
@@ -506,49 +503,46 @@
     <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/273639889.htm</t>
   </si>
   <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/cambronne-garibaldi/274316193.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273630989.htm</t>
+  </si>
+  <si>
+    <t>1 080 € /mois</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/vanves-92/centre-ancien/267289923.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/273639857.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/vaugirard-parc-des-expositions/271629933.htm</t>
+  </si>
+  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-17eme-75/ternes-maillot/273186559.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/cambronne-garibaldi/274316193.htm</t>
-  </si>
-  <si>
-    <t>1 941 € /mois</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/issy-les-moulineaux-92/273103027.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273630989.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/273639857.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/271456951.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/vaugirard-parc-des-expositions/271629933.htm</t>
-  </si>
-  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-18eme-75/goutte-d-or-chateau-rouge/274249093.htm</t>
   </si>
   <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639893.htm</t>
   </si>
   <si>
-    <t>Paris 9ème</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-9eme-75/trudaine-maubeuge/273938495.htm</t>
-  </si>
-  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/273089161.htm</t>
   </si>
   <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/198507995.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/muette-nord/259385227.htm</t>
+  </si>
+  <si>
     <t>Prospector — Paris Listings</t>
   </si>
   <si>
-    <t>Generated: 07/07/2026, 14:37:55</t>
+    <t>Generated: 07/07/2026, 20:36:03</t>
   </si>
   <si>
     <t>Barnes: 100 listings</t>
@@ -1849,7 +1843,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="4">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -2757,31 +2751,31 @@
         <v>11</v>
       </c>
       <c r="B52" s="4">
-        <v>10600</v>
+        <v>11500</v>
       </c>
       <c r="C52" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" s="3">
         <v>3</v>
       </c>
       <c r="E52" s="3">
-        <v>214</v>
+        <v>160</v>
       </c>
       <c r="F52" s="5">
         <f>B52/E52</f>
       </c>
       <c r="G52" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>79</v>
@@ -2792,34 +2786,34 @@
         <v>11</v>
       </c>
       <c r="B53" s="4">
-        <v>10450</v>
+        <v>10600</v>
       </c>
       <c r="C53" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="3">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="F53" s="5">
         <f>B53/E53</f>
       </c>
       <c r="G53" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K53" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2827,7 +2821,7 @@
         <v>11</v>
       </c>
       <c r="B54" s="4">
-        <v>10000</v>
+        <v>10450</v>
       </c>
       <c r="C54" s="3">
         <v>3</v>
@@ -2836,22 +2830,22 @@
         <v>2</v>
       </c>
       <c r="E54" s="3">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F54" s="5">
         <f>B54/E54</f>
       </c>
       <c r="G54" s="3" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>82</v>
@@ -2865,19 +2859,19 @@
         <v>10000</v>
       </c>
       <c r="C55" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D55" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E55" s="3">
-        <v>220</v>
+        <v>153</v>
       </c>
       <c r="F55" s="5">
         <f>B55/E55</f>
       </c>
       <c r="G55" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>13</v>
@@ -2886,7 +2880,7 @@
         <v>14</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>83</v>
@@ -2900,28 +2894,28 @@
         <v>10000</v>
       </c>
       <c r="C56" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D56" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" s="3">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="F56" s="5">
         <f>B56/E56</f>
       </c>
       <c r="G56" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>84</v>
@@ -2932,28 +2926,28 @@
         <v>11</v>
       </c>
       <c r="B57" s="4">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="C57" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" s="3">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="F57" s="5">
         <f>B57/E57</f>
       </c>
       <c r="G57" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>13</v>
@@ -2967,16 +2961,16 @@
         <v>11</v>
       </c>
       <c r="B58" s="4">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="C58" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D58" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" s="3">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="F58" s="5">
         <f>B58/E58</f>
@@ -2991,7 +2985,7 @@
         <v>14</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>86</v>
@@ -3002,7 +2996,7 @@
         <v>11</v>
       </c>
       <c r="B59" s="4">
-        <v>9000</v>
+        <v>9800</v>
       </c>
       <c r="C59" s="3">
         <v>3</v>
@@ -3011,7 +3005,7 @@
         <v>3</v>
       </c>
       <c r="E59" s="3">
-        <v>163</v>
+        <v>241</v>
       </c>
       <c r="F59" s="5">
         <f>B59/E59</f>
@@ -3026,7 +3020,7 @@
         <v>14</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>87</v>
@@ -3037,22 +3031,22 @@
         <v>11</v>
       </c>
       <c r="B60" s="4">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="C60" s="3">
         <v>3</v>
       </c>
       <c r="D60" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="3">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F60" s="5">
         <f>B60/E60</f>
       </c>
       <c r="G60" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>13</v>
@@ -3061,7 +3055,7 @@
         <v>14</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>88</v>
@@ -3072,7 +3066,7 @@
         <v>11</v>
       </c>
       <c r="B61" s="4">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="C61" s="3">
         <v>3</v>
@@ -3081,7 +3075,7 @@
         <v>2</v>
       </c>
       <c r="E61" s="3">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="F61" s="5">
         <f>B61/E61</f>
@@ -3093,10 +3087,10 @@
         <v>13</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>89</v>
@@ -3107,22 +3101,22 @@
         <v>11</v>
       </c>
       <c r="B62" s="4">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="C62" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D62" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" s="3">
-        <v>231</v>
+        <v>104</v>
       </c>
       <c r="F62" s="5">
         <f>B62/E62</f>
       </c>
       <c r="G62" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>13</v>
@@ -3131,7 +3125,7 @@
         <v>13</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>90</v>
@@ -3145,28 +3139,28 @@
         <v>8500</v>
       </c>
       <c r="C63" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D63" s="3">
         <v>3</v>
       </c>
       <c r="E63" s="3">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="F63" s="5">
         <f>B63/E63</f>
       </c>
       <c r="G63" s="3" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>91</v>
@@ -3177,31 +3171,31 @@
         <v>11</v>
       </c>
       <c r="B64" s="4">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="C64" s="3">
         <v>3</v>
       </c>
       <c r="D64" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" s="3">
-        <v>238</v>
+        <v>153</v>
       </c>
       <c r="F64" s="5">
         <f>B64/E64</f>
       </c>
       <c r="G64" s="3" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>92</v>
@@ -3212,16 +3206,16 @@
         <v>11</v>
       </c>
       <c r="B65" s="4">
-        <v>8000</v>
+        <v>8400</v>
       </c>
       <c r="C65" s="3">
         <v>3</v>
       </c>
       <c r="D65" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" s="3">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="F65" s="5">
         <f>B65/E65</f>
@@ -3230,13 +3224,13 @@
         <v>41</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>93</v>
@@ -3247,16 +3241,16 @@
         <v>11</v>
       </c>
       <c r="B66" s="4">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="C66" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D66" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E66" s="3">
-        <v>242</v>
+        <v>193</v>
       </c>
       <c r="F66" s="5">
         <f>B66/E66</f>
@@ -3265,7 +3259,7 @@
         <v>41</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>14</v>
@@ -3282,25 +3276,25 @@
         <v>11</v>
       </c>
       <c r="B67" s="4">
-        <v>7400</v>
+        <v>7800</v>
       </c>
       <c r="C67" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D67" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E67" s="3">
-        <v>166</v>
+        <v>242</v>
       </c>
       <c r="F67" s="5">
         <f>B67/E67</f>
       </c>
       <c r="G67" s="3" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>14</v>
@@ -3317,25 +3311,25 @@
         <v>11</v>
       </c>
       <c r="B68" s="4">
-        <v>7000</v>
+        <v>7400</v>
       </c>
       <c r="C68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" s="3">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="F68" s="5">
         <f>B68/E68</f>
       </c>
       <c r="G68" s="3" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>14</v>
@@ -3352,7 +3346,7 @@
         <v>11</v>
       </c>
       <c r="B69" s="4">
-        <v>6950</v>
+        <v>7000</v>
       </c>
       <c r="C69" s="3">
         <v>2</v>
@@ -3361,13 +3355,13 @@
         <v>2</v>
       </c>
       <c r="E69" s="3">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="F69" s="5">
         <f>B69/E69</f>
       </c>
       <c r="G69" s="3" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>13</v>
@@ -3387,22 +3381,22 @@
         <v>11</v>
       </c>
       <c r="B70" s="4">
-        <v>6765</v>
+        <v>6950</v>
       </c>
       <c r="C70" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D70" s="3">
         <v>2</v>
       </c>
       <c r="E70" s="3">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F70" s="5">
         <f>B70/E70</f>
       </c>
       <c r="G70" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>13</v>
@@ -3422,28 +3416,28 @@
         <v>11</v>
       </c>
       <c r="B71" s="4">
-        <v>6550</v>
+        <v>6765</v>
       </c>
       <c r="C71" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D71" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" s="3">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="F71" s="5">
         <f>B71/E71</f>
       </c>
       <c r="G71" s="3" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>13</v>
@@ -3457,28 +3451,28 @@
         <v>11</v>
       </c>
       <c r="B72" s="4">
-        <v>6520</v>
+        <v>6550</v>
       </c>
       <c r="C72" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" s="3">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="F72" s="5">
         <f>B72/E72</f>
       </c>
       <c r="G72" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>13</v>
@@ -3492,31 +3486,31 @@
         <v>11</v>
       </c>
       <c r="B73" s="4">
-        <v>6500</v>
+        <v>6520</v>
       </c>
       <c r="C73" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" s="3">
         <v>2</v>
       </c>
       <c r="E73" s="3">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F73" s="5">
         <f>B73/E73</f>
       </c>
       <c r="G73" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>101</v>
@@ -3530,28 +3524,28 @@
         <v>6500</v>
       </c>
       <c r="C74" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" s="3">
         <v>2</v>
       </c>
       <c r="E74" s="3">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="F74" s="5">
         <f>B74/E74</f>
       </c>
       <c r="G74" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>102</v>
@@ -3565,25 +3559,25 @@
         <v>6500</v>
       </c>
       <c r="C75" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
       </c>
       <c r="E75" s="3">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F75" s="5">
         <f>B75/E75</f>
       </c>
       <c r="G75" s="3" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J75" s="3" t="s">
         <v>13</v>
@@ -3597,28 +3591,28 @@
         <v>11</v>
       </c>
       <c r="B76" s="4">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="C76" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="3">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="F76" s="5">
         <f>B76/E76</f>
       </c>
       <c r="G76" s="3" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>13</v>
@@ -3632,30 +3626,34 @@
         <v>11</v>
       </c>
       <c r="B77" s="4">
-        <v>5800</v>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
+        <v>6000</v>
+      </c>
+      <c r="C77" s="3">
+        <v>1</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1</v>
+      </c>
       <c r="E77" s="3">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="F77" s="5">
         <f>B77/E77</f>
       </c>
       <c r="G77" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K77" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3663,22 +3661,18 @@
         <v>11</v>
       </c>
       <c r="B78" s="4">
-        <v>5500</v>
-      </c>
-      <c r="C78" s="3">
-        <v>3</v>
-      </c>
-      <c r="D78" s="3">
-        <v>2</v>
-      </c>
+        <v>5800</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
       <c r="E78" s="3">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="F78" s="5">
         <f>B78/E78</f>
       </c>
       <c r="G78" s="3" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>13</v>
@@ -3736,19 +3730,19 @@
         <v>5500</v>
       </c>
       <c r="C80" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" s="3">
         <v>2</v>
       </c>
       <c r="E80" s="3">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="F80" s="5">
         <f>B80/E80</f>
       </c>
       <c r="G80" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>13</v>
@@ -3771,13 +3765,13 @@
         <v>5500</v>
       </c>
       <c r="C81" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
       </c>
       <c r="E81" s="3">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="F81" s="5">
         <f>B81/E81</f>
@@ -3792,7 +3786,7 @@
         <v>14</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>110</v>
@@ -3803,16 +3797,16 @@
         <v>11</v>
       </c>
       <c r="B82" s="4">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="C82" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" s="3">
         <v>2</v>
       </c>
       <c r="E82" s="3">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="F82" s="5">
         <f>B82/E82</f>
@@ -3824,10 +3818,10 @@
         <v>13</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>111</v>
@@ -3838,16 +3832,16 @@
         <v>11</v>
       </c>
       <c r="B83" s="4">
-        <v>5200</v>
+        <v>5400</v>
       </c>
       <c r="C83" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" s="3">
         <v>2</v>
       </c>
       <c r="E83" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F83" s="5">
         <f>B83/E83</f>
@@ -3859,7 +3853,7 @@
         <v>13</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>13</v>
@@ -3873,7 +3867,7 @@
         <v>11</v>
       </c>
       <c r="B84" s="4">
-        <v>5150</v>
+        <v>5200</v>
       </c>
       <c r="C84" s="3">
         <v>3</v>
@@ -3882,19 +3876,19 @@
         <v>2</v>
       </c>
       <c r="E84" s="3">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F84" s="5">
         <f>B84/E84</f>
       </c>
       <c r="G84" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J84" s="3" t="s">
         <v>13</v>
@@ -3908,7 +3902,7 @@
         <v>11</v>
       </c>
       <c r="B85" s="4">
-        <v>5073</v>
+        <v>5150</v>
       </c>
       <c r="C85" s="3">
         <v>3</v>
@@ -3917,19 +3911,19 @@
         <v>2</v>
       </c>
       <c r="E85" s="3">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F85" s="5">
         <f>B85/E85</f>
       </c>
       <c r="G85" s="3" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>13</v>
@@ -3943,25 +3937,25 @@
         <v>11</v>
       </c>
       <c r="B86" s="4">
-        <v>4900</v>
+        <v>5073</v>
       </c>
       <c r="C86" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86" s="3">
         <v>2</v>
       </c>
       <c r="E86" s="3">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="F86" s="5">
         <f>B86/E86</f>
       </c>
       <c r="G86" s="3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>14</v>
@@ -3978,31 +3972,31 @@
         <v>11</v>
       </c>
       <c r="B87" s="4">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="C87" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="3">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="F87" s="5">
         <f>B87/E87</f>
       </c>
       <c r="G87" s="3" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>14</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K87" s="3" t="s">
         <v>116</v>
@@ -4019,7 +4013,7 @@
         <v>3</v>
       </c>
       <c r="D88" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="3">
         <v>127</v>
@@ -4034,7 +4028,7 @@
         <v>13</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J88" s="3" t="s">
         <v>14</v>
@@ -4057,7 +4051,7 @@
         <v>2</v>
       </c>
       <c r="E89" s="3">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F89" s="5">
         <f>B89/E89</f>
@@ -4072,7 +4066,7 @@
         <v>13</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>118</v>
@@ -4086,13 +4080,13 @@
         <v>4800</v>
       </c>
       <c r="C90" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" s="3">
         <v>2</v>
       </c>
       <c r="E90" s="3">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="F90" s="5">
         <f>B90/E90</f>
@@ -4104,7 +4098,7 @@
         <v>13</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>13</v>
@@ -4118,28 +4112,28 @@
         <v>11</v>
       </c>
       <c r="B91" s="4">
-        <v>4500</v>
+        <v>4800</v>
       </c>
       <c r="C91" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" s="3">
         <v>2</v>
       </c>
       <c r="E91" s="3">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="F91" s="5">
         <f>B91/E91</f>
       </c>
       <c r="G91" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>13</v>
@@ -4153,7 +4147,7 @@
         <v>11</v>
       </c>
       <c r="B92" s="4">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="C92" s="3">
         <v>3</v>
@@ -4162,19 +4156,19 @@
         <v>2</v>
       </c>
       <c r="E92" s="3">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="F92" s="5">
         <f>B92/E92</f>
       </c>
       <c r="G92" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>13</v>
@@ -4188,7 +4182,7 @@
         <v>11</v>
       </c>
       <c r="B93" s="4">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="C93" s="3">
         <v>3</v>
@@ -4197,13 +4191,13 @@
         <v>2</v>
       </c>
       <c r="E93" s="3">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F93" s="5">
         <f>B93/E93</f>
       </c>
       <c r="G93" s="3" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>13</v>
@@ -4223,7 +4217,7 @@
         <v>11</v>
       </c>
       <c r="B94" s="4">
-        <v>4053</v>
+        <v>4200</v>
       </c>
       <c r="C94" s="3">
         <v>3</v>
@@ -4232,13 +4226,13 @@
         <v>2</v>
       </c>
       <c r="E94" s="3">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="F94" s="5">
         <f>B94/E94</f>
       </c>
       <c r="G94" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>13</v>
@@ -4247,7 +4241,7 @@
         <v>14</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>123</v>
@@ -4258,31 +4252,31 @@
         <v>11</v>
       </c>
       <c r="B95" s="4">
-        <v>3900</v>
+        <v>4053</v>
       </c>
       <c r="C95" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" s="3">
         <v>2</v>
       </c>
       <c r="E95" s="3">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="F95" s="5">
         <f>B95/E95</f>
       </c>
       <c r="G95" s="3" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K95" s="3" t="s">
         <v>124</v>
@@ -4296,19 +4290,19 @@
         <v>3900</v>
       </c>
       <c r="C96" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="3">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F96" s="5">
         <f>B96/E96</f>
       </c>
       <c r="G96" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>13</v>
@@ -4328,31 +4322,31 @@
         <v>11</v>
       </c>
       <c r="B97" s="4">
-        <v>3850</v>
+        <v>3900</v>
       </c>
       <c r="C97" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" s="3">
         <v>1</v>
       </c>
       <c r="E97" s="3">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="F97" s="5">
         <f>B97/E97</f>
       </c>
       <c r="G97" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K97" s="3" t="s">
         <v>126</v>
@@ -4363,22 +4357,22 @@
         <v>11</v>
       </c>
       <c r="B98" s="4">
-        <v>3750</v>
+        <v>3850</v>
       </c>
       <c r="C98" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D98" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="3">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="F98" s="5">
         <f>B98/E98</f>
       </c>
       <c r="G98" s="3" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>13</v>
@@ -4398,22 +4392,22 @@
         <v>11</v>
       </c>
       <c r="B99" s="4">
-        <v>3500</v>
+        <v>3750</v>
       </c>
       <c r="C99" s="3">
         <v>2</v>
       </c>
       <c r="D99" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="3">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F99" s="5">
         <f>B99/E99</f>
       </c>
       <c r="G99" s="3" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>13</v>
@@ -4422,7 +4416,7 @@
         <v>14</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K99" s="3" t="s">
         <v>128</v>
@@ -4436,13 +4430,13 @@
         <v>3500</v>
       </c>
       <c r="C100" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" s="3">
         <v>1</v>
       </c>
       <c r="E100" s="3">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F100" s="5">
         <f>B100/E100</f>
@@ -4451,13 +4445,13 @@
         <v>12</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>14</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>129</v>
@@ -4471,36 +4465,36 @@
         <v>3500</v>
       </c>
       <c r="C101" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D101" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="3">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="F101" s="5">
         <f>B101/E101</f>
       </c>
       <c r="G101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K101" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B102" s="4">
         <v>2200</v>
@@ -4518,24 +4512,24 @@
         <f>B102/E102</f>
       </c>
       <c r="G102" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K102" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="103" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B103" s="4">
         <v>7900</v>
@@ -4553,42 +4547,42 @@
         <f>B103/E103</f>
       </c>
       <c r="G103" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K103" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J103" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K103" s="3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="104" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B104" s="4">
-        <v>6330</v>
+        <v>4700</v>
       </c>
       <c r="C104" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D104" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="3">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F104" s="5">
         <f>B104/E104</f>
       </c>
       <c r="G104" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>13</v>
@@ -4597,33 +4591,33 @@
         <v>13</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B105" s="4">
-        <v>4700</v>
+        <v>2700</v>
       </c>
       <c r="C105" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D105" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="3">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="F105" s="5">
         <f>B105/E105</f>
       </c>
       <c r="G105" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>13</v>
@@ -4635,50 +4629,50 @@
         <v>14</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B106" s="4">
-        <v>2700</v>
+        <v>2250</v>
       </c>
       <c r="C106" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D106" s="3">
         <v>1</v>
       </c>
       <c r="E106" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F106" s="5">
         <f>B106/E106</f>
       </c>
       <c r="G106" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J106" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="107" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B107" s="4">
-        <v>2250</v>
+        <v>1890</v>
       </c>
       <c r="C107" s="3">
         <v>2</v>
@@ -4687,48 +4681,48 @@
         <v>1</v>
       </c>
       <c r="E107" s="3">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F107" s="5">
         <f>B107/E107</f>
       </c>
       <c r="G107" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="108" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B108" s="4">
-        <v>4150</v>
+        <v>1100</v>
       </c>
       <c r="C108" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D108" s="3">
         <v>1</v>
       </c>
       <c r="E108" s="3">
-        <v>109</v>
+        <v>9.4</v>
       </c>
       <c r="F108" s="5">
         <f>B108/E108</f>
       </c>
       <c r="G108" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>13</v>
@@ -4740,30 +4734,30 @@
         <v>13</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B109" s="4">
-        <v>1890</v>
+        <v>4150</v>
       </c>
       <c r="C109" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D109" s="3">
         <v>1</v>
       </c>
       <c r="E109" s="3">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="F109" s="5">
         <f>B109/E109</f>
       </c>
       <c r="G109" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>13</v>
@@ -4775,155 +4769,155 @@
         <v>13</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="110" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B110" s="4">
-        <v>1100</v>
+        <v>1220</v>
       </c>
       <c r="C110" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="3">
         <v>1</v>
       </c>
       <c r="E110" s="3">
-        <v>9.4</v>
+        <v>37.9</v>
       </c>
       <c r="F110" s="5">
         <f>B110/E110</f>
       </c>
       <c r="G110" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J110" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="111" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B111" s="4">
-        <v>1525</v>
+        <v>1100</v>
       </c>
       <c r="C111" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111" s="3">
         <v>1</v>
       </c>
       <c r="E111" s="3">
-        <v>66.1</v>
+        <v>10.7</v>
       </c>
       <c r="F111" s="5">
         <f>B111/E111</f>
       </c>
       <c r="G111" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B112" s="4">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="C112" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" s="3">
         <v>1</v>
       </c>
       <c r="E112" s="3">
-        <v>10.7</v>
+        <v>57</v>
       </c>
       <c r="F112" s="5">
         <f>B112/E112</f>
       </c>
       <c r="G112" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="113" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B113" s="4">
-        <v>2100</v>
+        <v>6330</v>
       </c>
       <c r="C113" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113" s="3">
         <v>1</v>
       </c>
       <c r="E113" s="3">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="F113" s="5">
         <f>B113/E113</f>
       </c>
       <c r="G113" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K113" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J113" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K113" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B114" s="4">
-        <v>1603</v>
+        <v>2000</v>
       </c>
       <c r="C114" s="3">
         <v>2</v>
@@ -4932,13 +4926,13 @@
         <v>1</v>
       </c>
       <c r="E114" s="3">
-        <v>48</v>
+        <v>39.6</v>
       </c>
       <c r="F114" s="5">
         <f>B114/E114</f>
       </c>
       <c r="G114" s="3" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>13</v>
@@ -4950,15 +4944,15 @@
         <v>13</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="115" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B115" s="4">
-        <v>2200</v>
+        <v>1603</v>
       </c>
       <c r="C115" s="3">
         <v>2</v>
@@ -4967,13 +4961,13 @@
         <v>1</v>
       </c>
       <c r="E115" s="3">
-        <v>39.6</v>
+        <v>48</v>
       </c>
       <c r="F115" s="5">
         <f>B115/E115</f>
       </c>
       <c r="G115" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>13</v>
@@ -4985,15 +4979,15 @@
         <v>13</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="116" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B116" s="4">
-        <v>162190</v>
+        <v>162200</v>
       </c>
       <c r="C116" s="3">
         <v>2</v>
@@ -5008,24 +5002,24 @@
         <f>B116/E116</f>
       </c>
       <c r="G116" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K116" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K116" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B117" s="4">
         <v>3650</v>
@@ -5043,7 +5037,7 @@
         <f>B117/E117</f>
       </c>
       <c r="G117" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>13</v>
@@ -5055,12 +5049,12 @@
         <v>14</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="118" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B118" s="4">
         <v>7250</v>
@@ -5078,24 +5072,24 @@
         <f>B118/E118</f>
       </c>
       <c r="G118" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K118" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J118" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K118" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B119" s="4">
         <v>1500</v>
@@ -5113,24 +5107,24 @@
         <f>B119/E119</f>
       </c>
       <c r="G119" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K119" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J119" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K119" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="120" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B120" s="4">
         <v>8900</v>
@@ -5148,24 +5142,24 @@
         <f>B120/E120</f>
       </c>
       <c r="G120" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K120" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J120" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K120" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="121" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B121" s="4">
         <v>1100</v>
@@ -5183,7 +5177,7 @@
         <f>B121/E121</f>
       </c>
       <c r="G121" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>13</v>
@@ -5195,30 +5189,30 @@
         <v>13</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="122" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B122" s="4">
-        <v>2850</v>
+        <v>2985</v>
       </c>
       <c r="C122" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D122" s="3">
         <v>1</v>
       </c>
       <c r="E122" s="3">
-        <v>80</v>
+        <v>89.6</v>
       </c>
       <c r="F122" s="5">
         <f>B122/E122</f>
       </c>
       <c r="G122" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>13</v>
@@ -5230,30 +5224,30 @@
         <v>14</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="123" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B123" s="4">
-        <v>2985</v>
+        <v>1200</v>
       </c>
       <c r="C123" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D123" s="3">
         <v>1</v>
       </c>
       <c r="E123" s="3">
-        <v>89.6</v>
+        <v>12.3</v>
       </c>
       <c r="F123" s="5">
         <f>B123/E123</f>
       </c>
       <c r="G123" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>13</v>
@@ -5262,50 +5256,48 @@
         <v>13</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="124" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B124" s="4">
-        <v>1941</v>
+        <v>1080</v>
       </c>
       <c r="C124" s="3">
-        <v>3</v>
-      </c>
-      <c r="D124" s="3">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D124" s="3"/>
       <c r="E124" s="3">
-        <v>65.1</v>
+        <v>31</v>
       </c>
       <c r="F124" s="5">
         <f>B124/E124</f>
       </c>
       <c r="G124" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K124" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I124" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J124" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K124" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="125" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B125" s="4">
         <v>1200</v>
@@ -5317,33 +5309,33 @@
         <v>1</v>
       </c>
       <c r="E125" s="3">
-        <v>12.3</v>
+        <v>13.6</v>
       </c>
       <c r="F125" s="5">
         <f>B125/E125</f>
       </c>
       <c r="G125" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J125" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="126" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B126" s="4">
-        <v>1200</v>
+        <v>1420</v>
       </c>
       <c r="C126" s="3">
         <v>1</v>
@@ -5352,33 +5344,33 @@
         <v>1</v>
       </c>
       <c r="E126" s="3">
-        <v>13.6</v>
+        <v>37</v>
       </c>
       <c r="F126" s="5">
         <f>B126/E126</f>
       </c>
       <c r="G126" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="127" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B127" s="4">
-        <v>1850</v>
+        <v>2850</v>
       </c>
       <c r="C127" s="3">
         <v>2</v>
@@ -5387,118 +5379,118 @@
         <v>1</v>
       </c>
       <c r="E127" s="3">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="F127" s="5">
         <f>B127/E127</f>
       </c>
       <c r="G127" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J127" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="128" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B128" s="4">
-        <v>1420</v>
+        <v>1175</v>
       </c>
       <c r="C128" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" s="3">
         <v>1</v>
       </c>
       <c r="E128" s="3">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F128" s="5">
         <f>B128/E128</f>
       </c>
       <c r="G128" s="3" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="129" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B129" s="4">
-        <v>1175</v>
+        <v>1255</v>
       </c>
       <c r="C129" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E129" s="3">
-        <v>33</v>
+        <v>15.3</v>
       </c>
       <c r="F129" s="5">
         <f>B129/E129</f>
       </c>
       <c r="G129" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J129" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="130" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B130" s="4">
-        <v>1255</v>
+        <v>2095</v>
       </c>
       <c r="C130" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E130" s="3">
-        <v>15.3</v>
+        <v>55</v>
       </c>
       <c r="F130" s="5">
         <f>B130/E130</f>
       </c>
       <c r="G130" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>13</v>
@@ -5507,33 +5499,33 @@
         <v>13</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="131" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B131" s="4">
-        <v>4500</v>
+        <v>2705</v>
       </c>
       <c r="C131" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D131" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E131" s="3">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="F131" s="5">
         <f>B131/E131</f>
       </c>
       <c r="G131" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="H131" s="3" t="s">
         <v>13</v>
@@ -5545,15 +5537,15 @@
         <v>13</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="132" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B132" s="4">
-        <v>2095</v>
+        <v>2985</v>
       </c>
       <c r="C132" s="3">
         <v>2</v>
@@ -5562,25 +5554,25 @@
         <v>1</v>
       </c>
       <c r="E132" s="3">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F132" s="5">
         <f>B132/E132</f>
       </c>
       <c r="G132" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -5600,22 +5592,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="524">
   <si>
     <t>Source</t>
   </si>
@@ -779,15 +779,15 @@
     <t>https://www.seloger.com/annonces/locations/appartement/paris-7eme-75/ecole-militaire/274381299.htm</t>
   </si>
   <si>
+    <t>1 / 29</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/neuilly-sur-seine-92/ile-de-la-jatte-parc-d-orleans/255050063.htm</t>
+  </si>
+  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273630989.htm</t>
   </si>
   <si>
-    <t>1 / 29</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/neuilly-sur-seine-92/ile-de-la-jatte-parc-d-orleans/255050063.htm</t>
-  </si>
-  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639893.htm</t>
   </si>
   <si>
@@ -804,9 +804,6 @@
   </si>
   <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/alleray-procession/270367951.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273630981.htm</t>
   </si>
   <si>
     <t>Book-a-Flat</t>
@@ -1053,7 +1050,7 @@
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/silly-gallieni/270998099.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-7eme-75/gros-caillou/268989177.htm</t>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273950887.htm</t>
   </si>
   <si>
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/parchamp-albert-kahn/268308221.htm</t>
@@ -1092,7 +1089,7 @@
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/vaillant-sembat/274773159.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/chaillot/269929907.htm</t>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/273639877.htm</t>
   </si>
   <si>
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/vaillant-sembat/272325469.htm</t>
@@ -1119,6 +1116,102 @@
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/reine-mairie/273705839.htm</t>
   </si>
   <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/mairie/273842041.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/264422657.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/274796827.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/274647305.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/274456853.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/274411689.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/la-verboise/274572509.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/mairie/273650489.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/mairie/274724371.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/saint-cloud-92/montretout/274045583.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687835.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/levallois-perret-92/georges-pompidou/273688395.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273688087.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687001.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687923.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687457.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687965.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/courbevoie-92/gambetta/273687845.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687773.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687087.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687463.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687359.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687915.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/rueil-malmaison-92/rueil-sur-seine-plaine-gare/274819647.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273686995.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/clichy-92/entree-de-ville/273608851.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687861.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273688091.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/clichy-92/centre-ville/273687807.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687905.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687921.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/asnieres-sur-seine-92/bac-becon-flachat-colombes/273687675.htm</t>
+  </si>
+  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/centre/273936385.htm</t>
   </si>
   <si>
@@ -1170,33 +1263,33 @@
     <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/lac-inferieur/273469557.htm</t>
   </si>
   <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/sud-rer/26EE9DX232RE.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/273926621.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/centre/274390713.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/274534687.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/272329211.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/chatou-78/273770183.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/sud-rer/26QLQY6X6X6G.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/lac-inferieur/26QMSAV3PH69.htm</t>
+  </si>
+  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/272581173.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/sud-rer/26EE9DX232RE.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/273926621.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/centre/274390713.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/274534687.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/chatou-78/273770183.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/272329211.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/sud-rer/26QLQY6X6X6G.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/lac-inferieur/26QMSAV3PH69.htm</t>
-  </si>
-  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/ibis/272330141.htm</t>
   </si>
   <si>
@@ -1305,10 +1398,76 @@
     <t>https://www.seloger.com/annonces/locations/appartement/saint-germain-en-laye-78/armagis/273546285.htm</t>
   </si>
   <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/saint-germain-des-pres/241342323.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/monnaie/274576347.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/saint-placide/274578193.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/monnaie/274575585.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/notre-dame-des-champs/274576073.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274577585.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/emeriau-zola/263512653.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/268322589.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/monnaie/264585199.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/176042961.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/268317627.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/249315871.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/saint-germain-des-pres/238478807.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/saint-placide/274722185.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/rennes/273957065.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/272959381.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274081961.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/274712487.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/odeon/272282681.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274588633.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273754065.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/notre-dame-des-champs/273467065.htm</t>
+  </si>
+  <si>
     <t>Prospector — Paris Listings</t>
   </si>
   <si>
-    <t>Generated: 13/07/2026, 15:26:51</t>
+    <t>Generated: 13/07/2026, 15:37:06</t>
   </si>
   <si>
     <t>Barnes: 100 listings</t>
@@ -1320,10 +1479,7 @@
     <t>Junot: 17 listings</t>
   </si>
   <si>
-    <t>SeLoger: 27 listings</t>
-  </si>
-  <si>
-    <t>SeLoger-Suburbs: FAILED — Timed out after 300000ms: SeLoger-Suburbs scrape</t>
+    <t>SeLoger: 26 listings</t>
   </si>
   <si>
     <t>Book-a-Flat: 32 listings</t>
@@ -1335,7 +1491,7 @@
     <t>SeLoger-Suburb-boulogne-billancourt: 31 listings</t>
   </si>
   <si>
-    <t>SeLoger-Suburb-garches: 0 listings</t>
+    <t>SeLoger-Suburb-garches: 32 listings</t>
   </si>
   <si>
     <t>SeLoger-Suburb-le-vesinet: 31 listings</t>
@@ -1419,7 +1575,7 @@
     <t>SeLoger-Paris-5e: 0 listings</t>
   </si>
   <si>
-    <t>SeLoger-Paris-6e: 0 listings</t>
+    <t>SeLoger-Paris-6e: 22 listings</t>
   </si>
   <si>
     <t>SeLoger-Paris-7e: 0 listings</t>
@@ -1438,7 +1594,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot; €&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1461,10 +1617,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFCC0000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -1493,7 +1645,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1501,7 +1653,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1841,7 +1992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K335"/>
+  <dimension ref="A1:K388"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -8411,22 +8562,22 @@
         <v>227</v>
       </c>
       <c r="B190" s="3">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="C190" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D190" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E190" s="2">
-        <v>12.3</v>
+        <v>90</v>
       </c>
       <c r="F190" s="4">
         <f>B190/E190</f>
       </c>
       <c r="G190" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>13</v>
@@ -8435,10 +8586,10 @@
         <v>13</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="191" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8446,22 +8597,22 @@
         <v>227</v>
       </c>
       <c r="B191" s="3">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="C191" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D191" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E191" s="2">
-        <v>90</v>
+        <v>12.3</v>
       </c>
       <c r="F191" s="4">
         <f>B191/E191</f>
       </c>
       <c r="G191" s="2" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>13</v>
@@ -8470,7 +8621,7 @@
         <v>13</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K191" s="2" t="s">
         <v>257</v>
@@ -8683,58 +8834,56 @@
     </row>
     <row r="198" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="B198" s="3">
-        <v>200</v>
+        <v>50000</v>
       </c>
       <c r="C198" s="2">
-        <v>1</v>
-      </c>
-      <c r="D198" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D198" s="2"/>
       <c r="E198" s="2">
-        <v>12.3</v>
+        <v>450</v>
       </c>
       <c r="F198" s="4">
         <f>B198/E198</f>
       </c>
       <c r="G198" s="2" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="199" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B199" s="3">
-        <v>50000</v>
+        <v>18000</v>
       </c>
       <c r="C199" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" s="2">
-        <v>450</v>
+        <v>247</v>
       </c>
       <c r="F199" s="4">
         <f>B199/E199</f>
       </c>
       <c r="G199" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>21</v>
@@ -8751,23 +8900,23 @@
     </row>
     <row r="200" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B200" s="3">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="C200" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" s="2">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="F200" s="4">
         <f>B200/E200</f>
       </c>
       <c r="G200" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>21</v>
@@ -8779,28 +8928,28 @@
         <v>21</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="201" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B201" s="3">
-        <v>16000</v>
+        <v>11000</v>
       </c>
       <c r="C201" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" s="2">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="F201" s="4">
         <f>B201/E201</f>
       </c>
       <c r="G201" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>21</v>
@@ -8812,28 +8961,28 @@
         <v>21</v>
       </c>
       <c r="K201" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="202" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B202" s="3">
-        <v>11000</v>
+        <v>10500</v>
       </c>
       <c r="C202" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" s="2">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="F202" s="4">
         <f>B202/E202</f>
       </c>
       <c r="G202" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>21</v>
@@ -8845,28 +8994,28 @@
         <v>21</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="203" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B203" s="3">
-        <v>10500</v>
+        <v>10000</v>
       </c>
       <c r="C203" s="2">
         <v>3</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" s="2">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F203" s="4">
         <f>B203/E203</f>
       </c>
       <c r="G203" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>21</v>
@@ -8878,28 +9027,28 @@
         <v>21</v>
       </c>
       <c r="K203" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="204" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B204" s="3">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="C204" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" s="2">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="F204" s="4">
         <f>B204/E204</f>
       </c>
       <c r="G204" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>21</v>
@@ -8916,23 +9065,23 @@
     </row>
     <row r="205" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B205" s="3">
-        <v>9000</v>
+        <v>6300</v>
       </c>
       <c r="C205" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F205" s="4">
         <f>B205/E205</f>
       </c>
       <c r="G205" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>21</v>
@@ -8944,28 +9093,28 @@
         <v>21</v>
       </c>
       <c r="K205" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="206" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B206" s="3">
-        <v>6300</v>
+        <v>5250</v>
       </c>
       <c r="C206" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" s="2">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="F206" s="4">
         <f>B206/E206</f>
       </c>
       <c r="G206" s="2" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>21</v>
@@ -8982,23 +9131,23 @@
     </row>
     <row r="207" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B207" s="3">
-        <v>5250</v>
+        <v>5200</v>
       </c>
       <c r="C207" s="2">
         <v>2</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" s="2">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F207" s="4">
         <f>B207/E207</f>
       </c>
       <c r="G207" s="2" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>21</v>
@@ -9010,28 +9159,28 @@
         <v>21</v>
       </c>
       <c r="K207" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="208" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B208" s="3">
-        <v>5200</v>
+        <v>4545</v>
       </c>
       <c r="C208" s="2">
         <v>2</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" s="2">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F208" s="4">
         <f>B208/E208</f>
       </c>
       <c r="G208" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>21</v>
@@ -9048,23 +9197,23 @@
     </row>
     <row r="209" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B209" s="3">
-        <v>4545</v>
+        <v>4300</v>
       </c>
       <c r="C209" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" s="2">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="F209" s="4">
         <f>B209/E209</f>
       </c>
       <c r="G209" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>21</v>
@@ -9076,28 +9225,28 @@
         <v>21</v>
       </c>
       <c r="K209" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="210" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B210" s="3">
-        <v>4300</v>
+        <v>3950</v>
       </c>
       <c r="C210" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" s="2">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F210" s="4">
         <f>B210/E210</f>
       </c>
       <c r="G210" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>21</v>
@@ -9114,23 +9263,23 @@
     </row>
     <row r="211" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B211" s="3">
-        <v>3950</v>
+        <v>3800</v>
       </c>
       <c r="C211" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F211" s="4">
         <f>B211/E211</f>
       </c>
       <c r="G211" s="2" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>21</v>
@@ -9147,23 +9296,23 @@
     </row>
     <row r="212" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B212" s="3">
-        <v>3800</v>
+        <v>3750</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F212" s="4">
         <f>B212/E212</f>
       </c>
       <c r="G212" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>21</v>
@@ -9175,28 +9324,28 @@
         <v>21</v>
       </c>
       <c r="K212" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="213" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B213" s="3">
-        <v>3750</v>
+        <v>3490</v>
       </c>
       <c r="C213" s="2">
         <v>1</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" s="2">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="F213" s="4">
         <f>B213/E213</f>
       </c>
       <c r="G213" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>21</v>
@@ -9208,28 +9357,28 @@
         <v>21</v>
       </c>
       <c r="K213" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="214" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B214" s="3">
-        <v>3490</v>
+        <v>3300</v>
       </c>
       <c r="C214" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" s="2">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="F214" s="4">
         <f>B214/E214</f>
       </c>
       <c r="G214" s="2" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>21</v>
@@ -9246,23 +9395,23 @@
     </row>
     <row r="215" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B215" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="C215" s="2">
         <v>2</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F215" s="4">
         <f>B215/E215</f>
       </c>
       <c r="G215" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>21</v>
@@ -9274,28 +9423,28 @@
         <v>21</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="216" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B216" s="3">
-        <v>3200</v>
+        <v>2950</v>
       </c>
       <c r="C216" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" s="2">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="F216" s="4">
         <f>B216/E216</f>
       </c>
       <c r="G216" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>21</v>
@@ -9312,23 +9461,23 @@
     </row>
     <row r="217" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B217" s="3">
-        <v>2950</v>
+        <v>2800</v>
       </c>
       <c r="C217" s="2">
         <v>1</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" s="2">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F217" s="4">
         <f>B217/E217</f>
       </c>
       <c r="G217" s="2" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>21</v>
@@ -9345,23 +9494,23 @@
     </row>
     <row r="218" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B218" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="C218" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F218" s="4">
         <f>B218/E218</f>
       </c>
       <c r="G218" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>21</v>
@@ -9378,23 +9527,23 @@
     </row>
     <row r="219" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B219" s="3">
-        <v>2700</v>
+        <v>2610</v>
       </c>
       <c r="C219" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" s="2">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F219" s="4">
         <f>B219/E219</f>
       </c>
       <c r="G219" s="2" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>21</v>
@@ -9411,23 +9560,23 @@
     </row>
     <row r="220" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B220" s="3">
-        <v>2610</v>
+        <v>2550</v>
       </c>
       <c r="C220" s="2">
         <v>1</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F220" s="4">
         <f>B220/E220</f>
       </c>
       <c r="G220" s="2" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>21</v>
@@ -9444,23 +9593,23 @@
     </row>
     <row r="221" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B221" s="3">
-        <v>2550</v>
+        <v>2520</v>
       </c>
       <c r="C221" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F221" s="4">
         <f>B221/E221</f>
       </c>
       <c r="G221" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>21</v>
@@ -9477,23 +9626,23 @@
     </row>
     <row r="222" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B222" s="3">
-        <v>2520</v>
+        <v>2100</v>
       </c>
       <c r="C222" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" s="2">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="F222" s="4">
         <f>B222/E222</f>
       </c>
       <c r="G222" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>21</v>
@@ -9510,7 +9659,7 @@
     </row>
     <row r="223" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B223" s="3">
         <v>2100</v>
@@ -9520,13 +9669,13 @@
       </c>
       <c r="D223" s="2"/>
       <c r="E223" s="2">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="F223" s="4">
         <f>B223/E223</f>
       </c>
       <c r="G223" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>21</v>
@@ -9543,7 +9692,7 @@
     </row>
     <row r="224" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B224" s="3">
         <v>2100</v>
@@ -9553,13 +9702,13 @@
       </c>
       <c r="D224" s="2"/>
       <c r="E224" s="2">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="F224" s="4">
         <f>B224/E224</f>
       </c>
       <c r="G224" s="2" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>21</v>
@@ -9571,28 +9720,28 @@
         <v>21</v>
       </c>
       <c r="K224" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="225" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B225" s="3">
-        <v>2100</v>
+        <v>1975</v>
       </c>
       <c r="C225" s="2">
         <v>1</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F225" s="4">
         <f>B225/E225</f>
       </c>
       <c r="G225" s="2" t="s">
-        <v>303</v>
+        <v>265</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>21</v>
@@ -9609,23 +9758,23 @@
     </row>
     <row r="226" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B226" s="3">
-        <v>1975</v>
+        <v>1961</v>
       </c>
       <c r="C226" s="2">
         <v>1</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F226" s="4">
         <f>B226/E226</f>
       </c>
       <c r="G226" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>21</v>
@@ -9642,23 +9791,23 @@
     </row>
     <row r="227" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B227" s="3">
-        <v>1961</v>
+        <v>1950</v>
       </c>
       <c r="C227" s="2">
         <v>1</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F227" s="4">
         <f>B227/E227</f>
       </c>
       <c r="G227" s="2" t="s">
-        <v>266</v>
+        <v>306</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>21</v>
@@ -9670,28 +9819,26 @@
         <v>21</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="228" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B228" s="3">
-        <v>1950</v>
-      </c>
-      <c r="C228" s="2">
-        <v>1</v>
-      </c>
+        <v>1415</v>
+      </c>
+      <c r="C228" s="2"/>
       <c r="D228" s="2"/>
       <c r="E228" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F228" s="4">
         <f>B228/E228</f>
       </c>
       <c r="G228" s="2" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>21</v>
@@ -9708,21 +9855,21 @@
     </row>
     <row r="229" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B229" s="3">
-        <v>1415</v>
+        <v>1131</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
       <c r="E229" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F229" s="4">
         <f>B229/E229</f>
       </c>
       <c r="G229" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>21</v>
@@ -9734,26 +9881,26 @@
         <v>21</v>
       </c>
       <c r="K229" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="230" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="B230" s="3">
-        <v>1131</v>
+        <v>825</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
       <c r="E230" s="2">
-        <v>16</v>
+        <v>17.13</v>
       </c>
       <c r="F230" s="4">
         <f>B230/E230</f>
       </c>
       <c r="G230" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>21</v>
@@ -9765,26 +9912,28 @@
         <v>21</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="231" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B231" s="3">
-        <v>825</v>
-      </c>
-      <c r="C231" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="C231" s="2">
+        <v>2</v>
+      </c>
       <c r="D231" s="2"/>
       <c r="E231" s="2">
-        <v>17.13</v>
+        <v>542.59</v>
       </c>
       <c r="F231" s="4">
         <f>B231/E231</f>
       </c>
       <c r="G231" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>21</v>
@@ -9796,28 +9945,28 @@
         <v>21</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="232" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B232" s="3">
-        <v>500</v>
+        <v>636</v>
       </c>
       <c r="C232" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" s="2">
-        <v>542.59</v>
+        <v>102.1</v>
       </c>
       <c r="F232" s="4">
         <f>B232/E232</f>
       </c>
       <c r="G232" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>21</v>
@@ -9829,28 +9978,28 @@
         <v>21</v>
       </c>
       <c r="K232" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="233" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B233" s="3">
-        <v>636</v>
+        <v>375</v>
       </c>
       <c r="C233" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" s="2">
-        <v>102.1</v>
+        <v>87.1</v>
       </c>
       <c r="F233" s="4">
         <f>B233/E233</f>
       </c>
       <c r="G233" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>21</v>
@@ -9862,28 +10011,26 @@
         <v>21</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="234" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B234" s="3">
-        <v>375</v>
-      </c>
-      <c r="C234" s="2">
-        <v>4</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C234" s="2"/>
       <c r="D234" s="2"/>
       <c r="E234" s="2">
-        <v>87.1</v>
+        <v>28.56</v>
       </c>
       <c r="F234" s="4">
         <f>B234/E234</f>
       </c>
       <c r="G234" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>21</v>
@@ -9895,26 +10042,28 @@
         <v>21</v>
       </c>
       <c r="K234" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="235" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B235" s="3">
-        <v>110</v>
-      </c>
-      <c r="C235" s="2"/>
+        <v>700</v>
+      </c>
+      <c r="C235" s="2">
+        <v>4</v>
+      </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2">
-        <v>28.56</v>
+        <v>98.3</v>
       </c>
       <c r="F235" s="4">
         <f>B235/E235</f>
       </c>
       <c r="G235" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>21</v>
@@ -9926,28 +10075,26 @@
         <v>21</v>
       </c>
       <c r="K235" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="236" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B236" s="3">
-        <v>700</v>
-      </c>
-      <c r="C236" s="2">
-        <v>4</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C236" s="2"/>
       <c r="D236" s="2"/>
       <c r="E236" s="2">
-        <v>98.3</v>
+        <v>423.29</v>
       </c>
       <c r="F236" s="4">
         <f>B236/E236</f>
       </c>
       <c r="G236" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>21</v>
@@ -9959,26 +10106,28 @@
         <v>21</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="237" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B237" s="3">
-        <v>15</v>
-      </c>
-      <c r="C237" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C237" s="2">
+        <v>5</v>
+      </c>
       <c r="D237" s="2"/>
       <c r="E237" s="2">
-        <v>423.29</v>
+        <v>3131.63</v>
       </c>
       <c r="F237" s="4">
         <f>B237/E237</f>
       </c>
       <c r="G237" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>21</v>
@@ -9990,28 +10139,28 @@
         <v>21</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="238" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B238" s="3">
-        <v>356</v>
+        <v>198</v>
       </c>
       <c r="C238" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" s="2">
-        <v>3131.63</v>
+        <v>40.54</v>
       </c>
       <c r="F238" s="4">
         <f>B238/E238</f>
       </c>
       <c r="G238" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>21</v>
@@ -10023,28 +10172,28 @@
         <v>21</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="239" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B239" s="3">
-        <v>198</v>
+        <v>330</v>
       </c>
       <c r="C239" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2">
-        <v>40.54</v>
+        <v>98.62</v>
       </c>
       <c r="F239" s="4">
         <f>B239/E239</f>
       </c>
       <c r="G239" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>21</v>
@@ -10056,28 +10205,28 @@
         <v>21</v>
       </c>
       <c r="K239" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="240" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B240" s="3">
-        <v>330</v>
+        <v>650</v>
       </c>
       <c r="C240" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" s="2">
-        <v>98.62</v>
+        <v>43.68</v>
       </c>
       <c r="F240" s="4">
         <f>B240/E240</f>
       </c>
       <c r="G240" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>21</v>
@@ -10089,28 +10238,26 @@
         <v>21</v>
       </c>
       <c r="K240" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="241" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B241" s="3">
-        <v>650</v>
-      </c>
-      <c r="C241" s="2">
-        <v>2</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="C241" s="2"/>
       <c r="D241" s="2"/>
       <c r="E241" s="2">
-        <v>43.68</v>
+        <v>20.06</v>
       </c>
       <c r="F241" s="4">
         <f>B241/E241</f>
       </c>
       <c r="G241" s="2" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>21</v>
@@ -10127,21 +10274,21 @@
     </row>
     <row r="242" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B242" s="3">
-        <v>875</v>
+        <v>800</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
       <c r="E242" s="2">
-        <v>20.06</v>
+        <v>23.62</v>
       </c>
       <c r="F242" s="4">
         <f>B242/E242</f>
       </c>
       <c r="G242" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>21</v>
@@ -10158,30 +10305,34 @@
     </row>
     <row r="243" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>312</v>
+        <v>227</v>
       </c>
       <c r="B243" s="3">
-        <v>800</v>
-      </c>
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="C243" s="2">
+        <v>2</v>
+      </c>
+      <c r="D243" s="2">
+        <v>1</v>
+      </c>
       <c r="E243" s="2">
-        <v>23.62</v>
+        <v>38</v>
       </c>
       <c r="F243" s="4">
         <f>B243/E243</f>
       </c>
       <c r="G243" s="2" t="s">
-        <v>313</v>
+        <v>157</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I243" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J243" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K243" s="2" t="s">
         <v>336</v>
@@ -10192,7 +10343,7 @@
         <v>227</v>
       </c>
       <c r="B244" s="3">
-        <v>300</v>
+        <v>635</v>
       </c>
       <c r="C244" s="2">
         <v>2</v>
@@ -10201,7 +10352,7 @@
         <v>1</v>
       </c>
       <c r="E244" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F244" s="4">
         <f>B244/E244</f>
@@ -10227,16 +10378,16 @@
         <v>227</v>
       </c>
       <c r="B245" s="3">
-        <v>635</v>
+        <v>849</v>
       </c>
       <c r="C245" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D245" s="2">
         <v>1</v>
       </c>
       <c r="E245" s="2">
-        <v>39</v>
+        <v>10.8</v>
       </c>
       <c r="F245" s="4">
         <f>B245/E245</f>
@@ -10248,10 +10399,10 @@
         <v>13</v>
       </c>
       <c r="I245" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J245" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K245" s="2" t="s">
         <v>338</v>
@@ -10271,7 +10422,7 @@
         <v>1</v>
       </c>
       <c r="E246" s="2">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="F246" s="4">
         <f>B246/E246</f>
@@ -10297,7 +10448,7 @@
         <v>227</v>
       </c>
       <c r="B247" s="3">
-        <v>849</v>
+        <v>899</v>
       </c>
       <c r="C247" s="2">
         <v>1</v>
@@ -10306,7 +10457,7 @@
         <v>1</v>
       </c>
       <c r="E247" s="2">
-        <v>10.7</v>
+        <v>12.6</v>
       </c>
       <c r="F247" s="4">
         <f>B247/E247</f>
@@ -10338,10 +10489,10 @@
         <v>1</v>
       </c>
       <c r="D248" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E248" s="2">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="F248" s="4">
         <f>B248/E248</f>
@@ -10367,16 +10518,16 @@
         <v>227</v>
       </c>
       <c r="B249" s="3">
-        <v>899</v>
+        <v>685</v>
       </c>
       <c r="C249" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E249" s="2">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="F249" s="4">
         <f>B249/E249</f>
@@ -10388,10 +10539,10 @@
         <v>13</v>
       </c>
       <c r="I249" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J249" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K249" s="2" t="s">
         <v>342</v>
@@ -10402,16 +10553,16 @@
         <v>227</v>
       </c>
       <c r="B250" s="3">
-        <v>685</v>
+        <v>899</v>
       </c>
       <c r="C250" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D250" s="2">
         <v>1</v>
       </c>
       <c r="E250" s="2">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F250" s="4">
         <f>B250/E250</f>
@@ -10423,10 +10574,10 @@
         <v>13</v>
       </c>
       <c r="I250" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J250" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K250" s="2" t="s">
         <v>343</v>
@@ -10437,16 +10588,16 @@
         <v>227</v>
       </c>
       <c r="B251" s="3">
-        <v>899</v>
+        <v>405</v>
       </c>
       <c r="C251" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D251" s="2">
         <v>1</v>
       </c>
       <c r="E251" s="2">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F251" s="4">
         <f>B251/E251</f>
@@ -10461,7 +10612,7 @@
         <v>13</v>
       </c>
       <c r="J251" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K251" s="2" t="s">
         <v>344</v>
@@ -10472,16 +10623,16 @@
         <v>227</v>
       </c>
       <c r="B252" s="3">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C252" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D252" s="2">
         <v>1</v>
       </c>
       <c r="E252" s="2">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="F252" s="4">
         <f>B252/E252</f>
@@ -10490,13 +10641,13 @@
         <v>157</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I252" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J252" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K252" s="2" t="s">
         <v>345</v>
@@ -10507,7 +10658,7 @@
         <v>227</v>
       </c>
       <c r="B253" s="3">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C253" s="2">
         <v>2</v>
@@ -10516,7 +10667,7 @@
         <v>1</v>
       </c>
       <c r="E253" s="2">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="F253" s="4">
         <f>B253/E253</f>
@@ -10525,7 +10676,7 @@
         <v>157</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I253" s="2" t="s">
         <v>13</v>
@@ -10542,7 +10693,7 @@
         <v>227</v>
       </c>
       <c r="B254" s="3">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="C254" s="2">
         <v>2</v>
@@ -10551,7 +10702,7 @@
         <v>1</v>
       </c>
       <c r="E254" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F254" s="4">
         <f>B254/E254</f>
@@ -10566,7 +10717,7 @@
         <v>13</v>
       </c>
       <c r="J254" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K254" s="2" t="s">
         <v>347</v>
@@ -10577,7 +10728,7 @@
         <v>227</v>
       </c>
       <c r="B255" s="3">
-        <v>900</v>
+        <v>550</v>
       </c>
       <c r="C255" s="2">
         <v>2</v>
@@ -10586,7 +10737,7 @@
         <v>1</v>
       </c>
       <c r="E255" s="2">
-        <v>53</v>
+        <v>37.2</v>
       </c>
       <c r="F255" s="4">
         <f>B255/E255</f>
@@ -10601,7 +10752,7 @@
         <v>13</v>
       </c>
       <c r="J255" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K255" s="2" t="s">
         <v>348</v>
@@ -10612,16 +10763,16 @@
         <v>227</v>
       </c>
       <c r="B256" s="3">
-        <v>550</v>
+        <v>150</v>
       </c>
       <c r="C256" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D256" s="2">
         <v>1</v>
       </c>
       <c r="E256" s="2">
-        <v>37.2</v>
+        <v>95.2</v>
       </c>
       <c r="F256" s="4">
         <f>B256/E256</f>
@@ -10633,10 +10784,10 @@
         <v>13</v>
       </c>
       <c r="I256" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J256" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K256" s="2" t="s">
         <v>349</v>
@@ -10647,16 +10798,16 @@
         <v>227</v>
       </c>
       <c r="B257" s="3">
-        <v>150</v>
+        <v>550</v>
       </c>
       <c r="C257" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D257" s="2">
         <v>1</v>
       </c>
       <c r="E257" s="2">
-        <v>95.2</v>
+        <v>69</v>
       </c>
       <c r="F257" s="4">
         <f>B257/E257</f>
@@ -10665,7 +10816,7 @@
         <v>157</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I257" s="2" t="s">
         <v>16</v>
@@ -10682,16 +10833,16 @@
         <v>227</v>
       </c>
       <c r="B258" s="3">
-        <v>550</v>
+        <v>32</v>
       </c>
       <c r="C258" s="2">
+        <v>4</v>
+      </c>
+      <c r="D258" s="2">
         <v>3</v>
       </c>
-      <c r="D258" s="2">
-        <v>1</v>
-      </c>
       <c r="E258" s="2">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F258" s="4">
         <f>B258/E258</f>
@@ -10700,7 +10851,7 @@
         <v>157</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I258" s="2" t="s">
         <v>16</v>
@@ -10717,16 +10868,16 @@
         <v>227</v>
       </c>
       <c r="B259" s="3">
-        <v>32</v>
+        <v>555</v>
       </c>
       <c r="C259" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D259" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E259" s="2">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="F259" s="4">
         <f>B259/E259</f>
@@ -10741,7 +10892,7 @@
         <v>16</v>
       </c>
       <c r="J259" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K259" s="2" t="s">
         <v>352</v>
@@ -10752,7 +10903,7 @@
         <v>227</v>
       </c>
       <c r="B260" s="3">
-        <v>555</v>
+        <v>500</v>
       </c>
       <c r="C260" s="2">
         <v>2</v>
@@ -10761,7 +10912,7 @@
         <v>1</v>
       </c>
       <c r="E260" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F260" s="4">
         <f>B260/E260</f>
@@ -10773,10 +10924,10 @@
         <v>13</v>
       </c>
       <c r="I260" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J260" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K260" s="2" t="s">
         <v>353</v>
@@ -10787,7 +10938,7 @@
         <v>227</v>
       </c>
       <c r="B261" s="3">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C261" s="2">
         <v>2</v>
@@ -10796,7 +10947,7 @@
         <v>1</v>
       </c>
       <c r="E261" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F261" s="4">
         <f>B261/E261</f>
@@ -10822,16 +10973,16 @@
         <v>227</v>
       </c>
       <c r="B262" s="3">
-        <v>490</v>
+        <v>200</v>
       </c>
       <c r="C262" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D262" s="2">
         <v>1</v>
       </c>
       <c r="E262" s="2">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="F262" s="4">
         <f>B262/E262</f>
@@ -10840,10 +10991,10 @@
         <v>157</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I262" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>13</v>
@@ -10857,16 +11008,16 @@
         <v>227</v>
       </c>
       <c r="B263" s="3">
-        <v>200</v>
+        <v>367</v>
       </c>
       <c r="C263" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D263" s="2">
         <v>1</v>
       </c>
       <c r="E263" s="2">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="F263" s="4">
         <f>B263/E263</f>
@@ -10875,7 +11026,7 @@
         <v>157</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I263" s="2" t="s">
         <v>16</v>
@@ -10892,7 +11043,7 @@
         <v>227</v>
       </c>
       <c r="B264" s="3">
-        <v>367</v>
+        <v>977</v>
       </c>
       <c r="C264" s="2">
         <v>2</v>
@@ -10901,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="E264" s="2">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="F264" s="4">
         <f>B264/E264</f>
@@ -10910,13 +11061,13 @@
         <v>157</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I264" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J264" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K264" s="2" t="s">
         <v>357</v>
@@ -10927,16 +11078,16 @@
         <v>227</v>
       </c>
       <c r="B265" s="3">
-        <v>977</v>
+        <v>300</v>
       </c>
       <c r="C265" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D265" s="2">
         <v>1</v>
       </c>
       <c r="E265" s="2">
-        <v>33</v>
+        <v>14.8</v>
       </c>
       <c r="F265" s="4">
         <f>B265/E265</f>
@@ -10945,13 +11096,13 @@
         <v>157</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I265" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J265" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K265" s="2" t="s">
         <v>358</v>
@@ -10962,16 +11113,14 @@
         <v>227</v>
       </c>
       <c r="B266" s="3">
-        <v>250</v>
+        <v>490</v>
       </c>
       <c r="C266" s="2">
-        <v>4</v>
-      </c>
-      <c r="D266" s="2">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D266" s="2"/>
       <c r="E266" s="2">
-        <v>100</v>
+        <v>39.3</v>
       </c>
       <c r="F266" s="4">
         <f>B266/E266</f>
@@ -10980,13 +11129,13 @@
         <v>157</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I266" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J266" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K266" s="2" t="s">
         <v>359</v>
@@ -10997,23 +11146,22 @@
         <v>227</v>
       </c>
       <c r="B267" s="3">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="C267" s="2">
-        <v>2</v>
-      </c>
-      <c r="D267" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="D267" s="2">
+        <v>1</v>
+      </c>
       <c r="E267" s="2">
-        <v>39.3</v>
-      </c>
-      <c r="F267" s="4">
-        <f>B267/E267</f>
+        <v>105</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I267" s="2" t="s">
         <v>16</v>
@@ -11030,25 +11178,28 @@
         <v>227</v>
       </c>
       <c r="B268" s="3">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="C268" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D268" s="2">
         <v>1</v>
       </c>
       <c r="E268" s="2">
-        <v>105</v>
+        <v>84</v>
+      </c>
+      <c r="F268" s="4">
+        <f>B268/E268</f>
       </c>
       <c r="G268" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I268" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>13</v>
@@ -11062,16 +11213,16 @@
         <v>227</v>
       </c>
       <c r="B269" s="3">
-        <v>750</v>
+        <v>914</v>
       </c>
       <c r="C269" s="2">
         <v>4</v>
       </c>
       <c r="D269" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E269" s="2">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F269" s="4">
         <f>B269/E269</f>
@@ -11080,7 +11231,7 @@
         <v>157</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I269" s="2" t="s">
         <v>13</v>
@@ -11097,16 +11248,16 @@
         <v>227</v>
       </c>
       <c r="B270" s="3">
-        <v>914</v>
+        <v>150</v>
       </c>
       <c r="C270" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D270" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E270" s="2">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F270" s="4">
         <f>B270/E270</f>
@@ -11118,7 +11269,7 @@
         <v>13</v>
       </c>
       <c r="I270" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>13</v>
@@ -11132,7 +11283,7 @@
         <v>227</v>
       </c>
       <c r="B271" s="3">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C271" s="2">
         <v>1</v>
@@ -11156,7 +11307,7 @@
         <v>16</v>
       </c>
       <c r="J271" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K271" s="2" t="s">
         <v>364</v>
@@ -11167,16 +11318,16 @@
         <v>227</v>
       </c>
       <c r="B272" s="3">
-        <v>100</v>
+        <v>525</v>
       </c>
       <c r="C272" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D272" s="2">
         <v>1</v>
       </c>
       <c r="E272" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="F272" s="4">
         <f>B272/E272</f>
@@ -11188,10 +11339,10 @@
         <v>13</v>
       </c>
       <c r="I272" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J272" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K272" s="2" t="s">
         <v>365</v>
@@ -11202,16 +11353,16 @@
         <v>227</v>
       </c>
       <c r="B273" s="3">
-        <v>525</v>
+        <v>280</v>
       </c>
       <c r="C273" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D273" s="2">
         <v>1</v>
       </c>
       <c r="E273" s="2">
-        <v>66</v>
+        <v>41.8</v>
       </c>
       <c r="F273" s="4">
         <f>B273/E273</f>
@@ -11237,31 +11388,31 @@
         <v>227</v>
       </c>
       <c r="B274" s="3">
-        <v>280</v>
+        <v>685</v>
       </c>
       <c r="C274" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D274" s="2">
         <v>1</v>
       </c>
       <c r="E274" s="2">
-        <v>41.8</v>
+        <v>61</v>
       </c>
       <c r="F274" s="4">
         <f>B274/E274</f>
       </c>
       <c r="G274" s="2" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I274" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J274" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K274" s="2" t="s">
         <v>367</v>
@@ -11272,31 +11423,31 @@
         <v>227</v>
       </c>
       <c r="B275" s="3">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="C275" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D275" s="2">
         <v>1</v>
       </c>
       <c r="E275" s="2">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="F275" s="4">
         <f>B275/E275</f>
       </c>
       <c r="G275" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I275" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J275" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K275" s="2" t="s">
         <v>368</v>
@@ -11307,31 +11458,31 @@
         <v>227</v>
       </c>
       <c r="B276" s="3">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C276" s="2">
+        <v>11</v>
+      </c>
+      <c r="D276" s="2">
         <v>3</v>
       </c>
-      <c r="D276" s="2">
-        <v>1</v>
-      </c>
       <c r="E276" s="2">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="F276" s="4">
         <f>B276/E276</f>
       </c>
       <c r="G276" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I276" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J276" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K276" s="2" t="s">
         <v>369</v>
@@ -11342,28 +11493,28 @@
         <v>227</v>
       </c>
       <c r="B277" s="3">
-        <v>400</v>
+        <v>890</v>
       </c>
       <c r="C277" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D277" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E277" s="2">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="F277" s="4">
         <f>B277/E277</f>
       </c>
       <c r="G277" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I277" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>13</v>
@@ -11377,31 +11528,31 @@
         <v>227</v>
       </c>
       <c r="B278" s="3">
-        <v>890</v>
+        <v>699</v>
       </c>
       <c r="C278" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D278" s="2">
         <v>1</v>
       </c>
       <c r="E278" s="2">
-        <v>87.2</v>
+        <v>78.1</v>
       </c>
       <c r="F278" s="4">
         <f>B278/E278</f>
       </c>
       <c r="G278" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I278" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J278" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K278" s="2" t="s">
         <v>371</v>
@@ -11412,31 +11563,31 @@
         <v>227</v>
       </c>
       <c r="B279" s="3">
-        <v>912</v>
+        <v>945</v>
       </c>
       <c r="C279" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D279" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E279" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F279" s="4">
         <f>B279/E279</f>
       </c>
       <c r="G279" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I279" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J279" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K279" s="2" t="s">
         <v>372</v>
@@ -11447,31 +11598,31 @@
         <v>227</v>
       </c>
       <c r="B280" s="3">
-        <v>400</v>
+        <v>870</v>
       </c>
       <c r="C280" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D280" s="2">
         <v>1</v>
       </c>
       <c r="E280" s="2">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F280" s="4">
         <f>B280/E280</f>
       </c>
       <c r="G280" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I280" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J280" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K280" s="2" t="s">
         <v>373</v>
@@ -11482,28 +11633,28 @@
         <v>227</v>
       </c>
       <c r="B281" s="3">
-        <v>275</v>
+        <v>830</v>
       </c>
       <c r="C281" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D281" s="2">
         <v>1</v>
       </c>
       <c r="E281" s="2">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="F281" s="4">
         <f>B281/E281</f>
       </c>
       <c r="G281" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I281" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>13</v>
@@ -11517,31 +11668,31 @@
         <v>227</v>
       </c>
       <c r="B282" s="3">
-        <v>990</v>
+        <v>53</v>
       </c>
       <c r="C282" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D282" s="2">
         <v>1</v>
       </c>
       <c r="E282" s="2">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="F282" s="4">
         <f>B282/E282</f>
       </c>
       <c r="G282" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I282" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J282" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K282" s="2" t="s">
         <v>375</v>
@@ -11552,22 +11703,22 @@
         <v>227</v>
       </c>
       <c r="B283" s="3">
-        <v>490</v>
+        <v>900</v>
       </c>
       <c r="C283" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D283" s="2">
         <v>1</v>
       </c>
       <c r="E283" s="2">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="F283" s="4">
         <f>B283/E283</f>
       </c>
       <c r="G283" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>13</v>
@@ -11587,28 +11738,28 @@
         <v>227</v>
       </c>
       <c r="B284" s="3">
-        <v>426</v>
+        <v>915</v>
       </c>
       <c r="C284" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D284" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E284" s="2">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="F284" s="4">
         <f>B284/E284</f>
       </c>
       <c r="G284" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I284" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>13</v>
@@ -11622,22 +11773,22 @@
         <v>227</v>
       </c>
       <c r="B285" s="3">
-        <v>400</v>
+        <v>945</v>
       </c>
       <c r="C285" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D285" s="2">
         <v>1</v>
       </c>
       <c r="E285" s="2">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="F285" s="4">
         <f>B285/E285</f>
       </c>
       <c r="G285" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>13</v>
@@ -11657,22 +11808,22 @@
         <v>227</v>
       </c>
       <c r="B286" s="3">
-        <v>570</v>
+        <v>775</v>
       </c>
       <c r="C286" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D286" s="2">
         <v>1</v>
       </c>
       <c r="E286" s="2">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F286" s="4">
         <f>B286/E286</f>
       </c>
       <c r="G286" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>13</v>
@@ -11681,7 +11832,7 @@
         <v>16</v>
       </c>
       <c r="J286" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K286" s="2" t="s">
         <v>379</v>
@@ -11692,28 +11843,28 @@
         <v>227</v>
       </c>
       <c r="B287" s="3">
-        <v>100</v>
+        <v>340</v>
       </c>
       <c r="C287" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D287" s="2">
         <v>1</v>
       </c>
       <c r="E287" s="2">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F287" s="4">
         <f>B287/E287</f>
       </c>
       <c r="G287" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I287" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>13</v>
@@ -11727,31 +11878,31 @@
         <v>227</v>
       </c>
       <c r="B288" s="3">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="C288" s="2">
+        <v>11</v>
+      </c>
+      <c r="D288" s="2">
         <v>3</v>
       </c>
-      <c r="D288" s="2">
-        <v>1</v>
-      </c>
       <c r="E288" s="2">
-        <v>71</v>
+        <v>220</v>
       </c>
       <c r="F288" s="4">
         <f>B288/E288</f>
       </c>
       <c r="G288" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I288" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J288" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K288" s="2" t="s">
         <v>381</v>
@@ -11762,7 +11913,7 @@
         <v>227</v>
       </c>
       <c r="B289" s="3">
-        <v>200</v>
+        <v>990</v>
       </c>
       <c r="C289" s="2">
         <v>4</v>
@@ -11771,19 +11922,19 @@
         <v>1</v>
       </c>
       <c r="E289" s="2">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F289" s="4">
         <f>B289/E289</f>
       </c>
       <c r="G289" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I289" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>13</v>
@@ -11797,28 +11948,28 @@
         <v>227</v>
       </c>
       <c r="B290" s="3">
-        <v>490</v>
+        <v>950</v>
       </c>
       <c r="C290" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D290" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E290" s="2">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F290" s="4">
         <f>B290/E290</f>
       </c>
       <c r="G290" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I290" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>13</v>
@@ -11832,28 +11983,28 @@
         <v>227</v>
       </c>
       <c r="B291" s="3">
-        <v>800</v>
+        <v>875</v>
       </c>
       <c r="C291" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D291" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E291" s="2">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="F291" s="4">
         <f>B291/E291</f>
       </c>
       <c r="G291" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I291" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>13</v>
@@ -11867,28 +12018,31 @@
         <v>227</v>
       </c>
       <c r="B292" s="3">
-        <v>0</v>
+        <v>955</v>
       </c>
       <c r="C292" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D292" s="2">
         <v>1</v>
       </c>
       <c r="E292" s="2">
-        <v>87</v>
+        <v>220</v>
+      </c>
+      <c r="F292" s="4">
+        <f>B292/E292</f>
       </c>
       <c r="G292" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I292" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J292" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K292" s="2" t="s">
         <v>385</v>
@@ -11899,22 +12053,22 @@
         <v>227</v>
       </c>
       <c r="B293" s="3">
-        <v>570</v>
+        <v>310</v>
       </c>
       <c r="C293" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D293" s="2">
         <v>1</v>
       </c>
       <c r="E293" s="2">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="F293" s="4">
         <f>B293/E293</f>
       </c>
       <c r="G293" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>13</v>
@@ -11923,7 +12077,7 @@
         <v>16</v>
       </c>
       <c r="J293" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K293" s="2" t="s">
         <v>386</v>
@@ -11934,22 +12088,22 @@
         <v>227</v>
       </c>
       <c r="B294" s="3">
-        <v>261</v>
+        <v>135</v>
       </c>
       <c r="C294" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D294" s="2">
         <v>1</v>
       </c>
       <c r="E294" s="2">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F294" s="4">
         <f>B294/E294</f>
       </c>
       <c r="G294" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>13</v>
@@ -11969,22 +12123,22 @@
         <v>227</v>
       </c>
       <c r="B295" s="3">
-        <v>38</v>
+        <v>995</v>
       </c>
       <c r="C295" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D295" s="2">
         <v>1</v>
       </c>
       <c r="E295" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F295" s="4">
         <f>B295/E295</f>
       </c>
       <c r="G295" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>13</v>
@@ -11993,7 +12147,7 @@
         <v>16</v>
       </c>
       <c r="J295" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K295" s="2" t="s">
         <v>388</v>
@@ -12004,26 +12158,28 @@
         <v>227</v>
       </c>
       <c r="B296" s="3">
-        <v>620</v>
+        <v>895</v>
       </c>
       <c r="C296" s="2">
-        <v>1</v>
-      </c>
-      <c r="D296" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="D296" s="2">
+        <v>1</v>
+      </c>
       <c r="E296" s="2">
-        <v>9.9</v>
+        <v>90</v>
       </c>
       <c r="F296" s="4">
         <f>B296/E296</f>
       </c>
       <c r="G296" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I296" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>13</v>
@@ -12037,31 +12193,31 @@
         <v>227</v>
       </c>
       <c r="B297" s="3">
-        <v>590</v>
+        <v>845</v>
       </c>
       <c r="C297" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D297" s="2">
         <v>1</v>
       </c>
       <c r="E297" s="2">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="F297" s="4">
         <f>B297/E297</f>
       </c>
       <c r="G297" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I297" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J297" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K297" s="2" t="s">
         <v>390</v>
@@ -12072,31 +12228,31 @@
         <v>227</v>
       </c>
       <c r="B298" s="3">
-        <v>967</v>
+        <v>990</v>
       </c>
       <c r="C298" s="2">
         <v>5</v>
       </c>
       <c r="D298" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E298" s="2">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="F298" s="4">
         <f>B298/E298</f>
       </c>
       <c r="G298" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I298" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J298" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K298" s="2" t="s">
         <v>391</v>
@@ -12107,25 +12263,25 @@
         <v>227</v>
       </c>
       <c r="B299" s="3">
-        <v>935</v>
+        <v>170</v>
       </c>
       <c r="C299" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D299" s="2">
         <v>1</v>
       </c>
       <c r="E299" s="2">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="F299" s="4">
         <f>B299/E299</f>
       </c>
       <c r="G299" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I299" s="2" t="s">
         <v>16</v>
@@ -12142,25 +12298,25 @@
         <v>227</v>
       </c>
       <c r="B300" s="3">
-        <v>900</v>
+        <v>975</v>
       </c>
       <c r="C300" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D300" s="2">
         <v>1</v>
       </c>
       <c r="E300" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="F300" s="4">
         <f>B300/E300</f>
       </c>
       <c r="G300" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I300" s="2" t="s">
         <v>13</v>
@@ -12177,22 +12333,22 @@
         <v>227</v>
       </c>
       <c r="B301" s="3">
-        <v>600</v>
+        <v>885</v>
       </c>
       <c r="C301" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D301" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E301" s="2">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="F301" s="4">
         <f>B301/E301</f>
       </c>
       <c r="G301" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>13</v>
@@ -12201,7 +12357,7 @@
         <v>16</v>
       </c>
       <c r="J301" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K301" s="2" t="s">
         <v>394</v>
@@ -12212,31 +12368,31 @@
         <v>227</v>
       </c>
       <c r="B302" s="3">
-        <v>253</v>
+        <v>910</v>
       </c>
       <c r="C302" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D302" s="2">
         <v>1</v>
       </c>
       <c r="E302" s="2">
-        <v>50.4</v>
+        <v>90</v>
       </c>
       <c r="F302" s="4">
         <f>B302/E302</f>
       </c>
       <c r="G302" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I302" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J302" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K302" s="2" t="s">
         <v>395</v>
@@ -12247,22 +12403,22 @@
         <v>227</v>
       </c>
       <c r="B303" s="3">
-        <v>700</v>
+        <v>985</v>
       </c>
       <c r="C303" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D303" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E303" s="2">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F303" s="4">
         <f>B303/E303</f>
       </c>
       <c r="G303" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>13</v>
@@ -12271,7 +12427,7 @@
         <v>13</v>
       </c>
       <c r="J303" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K303" s="2" t="s">
         <v>396</v>
@@ -12282,26 +12438,28 @@
         <v>227</v>
       </c>
       <c r="B304" s="3">
-        <v>795</v>
+        <v>955</v>
       </c>
       <c r="C304" s="2">
-        <v>1</v>
-      </c>
-      <c r="D304" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="D304" s="2">
+        <v>2</v>
+      </c>
       <c r="E304" s="2">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="F304" s="4">
         <f>B304/E304</f>
       </c>
       <c r="G304" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I304" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>13</v>
@@ -12315,22 +12473,22 @@
         <v>227</v>
       </c>
       <c r="B305" s="3">
-        <v>25</v>
+        <v>985</v>
       </c>
       <c r="C305" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D305" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E305" s="2">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="F305" s="4">
         <f>B305/E305</f>
       </c>
       <c r="G305" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>13</v>
@@ -12339,7 +12497,7 @@
         <v>16</v>
       </c>
       <c r="J305" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K305" s="2" t="s">
         <v>398</v>
@@ -12350,7 +12508,7 @@
         <v>227</v>
       </c>
       <c r="B306" s="3">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="C306" s="2">
         <v>2</v>
@@ -12359,25 +12517,25 @@
         <v>1</v>
       </c>
       <c r="E306" s="2">
-        <v>50.1</v>
+        <v>49</v>
       </c>
       <c r="F306" s="4">
         <f>B306/E306</f>
       </c>
       <c r="G306" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H306" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I306" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J306" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K306" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="H306" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I306" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J306" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K306" s="2" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="307" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12385,20 +12543,22 @@
         <v>227</v>
       </c>
       <c r="B307" s="3">
-        <v>404</v>
+        <v>912</v>
       </c>
       <c r="C307" s="2">
-        <v>2</v>
-      </c>
-      <c r="D307" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D307" s="2">
+        <v>1</v>
+      </c>
       <c r="E307" s="2">
-        <v>53.6</v>
+        <v>75</v>
       </c>
       <c r="F307" s="4">
         <f>B307/E307</f>
       </c>
       <c r="G307" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>13</v>
@@ -12407,10 +12567,10 @@
         <v>13</v>
       </c>
       <c r="J307" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K307" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="308" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12418,34 +12578,34 @@
         <v>227</v>
       </c>
       <c r="B308" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C308" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D308" s="2">
         <v>1</v>
       </c>
       <c r="E308" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F308" s="4">
         <f>B308/E308</f>
       </c>
       <c r="G308" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I308" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J308" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K308" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="309" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12453,19 +12613,22 @@
         <v>227</v>
       </c>
       <c r="B309" s="3">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="C309" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D309" s="2">
         <v>1</v>
       </c>
       <c r="E309" s="2">
-        <v>57</v>
+        <v>87.2</v>
+      </c>
+      <c r="F309" s="4">
+        <f>B309/E309</f>
       </c>
       <c r="G309" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>13</v>
@@ -12474,10 +12637,10 @@
         <v>16</v>
       </c>
       <c r="J309" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K309" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="310" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12485,7 +12648,7 @@
         <v>227</v>
       </c>
       <c r="B310" s="3">
-        <v>350</v>
+        <v>912</v>
       </c>
       <c r="C310" s="2">
         <v>3</v>
@@ -12494,13 +12657,13 @@
         <v>1</v>
       </c>
       <c r="E310" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F310" s="4">
         <f>B310/E310</f>
       </c>
       <c r="G310" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>13</v>
@@ -12512,7 +12675,7 @@
         <v>16</v>
       </c>
       <c r="K310" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="311" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12520,34 +12683,34 @@
         <v>227</v>
       </c>
       <c r="B311" s="3">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="C311" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D311" s="2">
         <v>1</v>
       </c>
       <c r="E311" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F311" s="4">
         <f>B311/E311</f>
       </c>
       <c r="G311" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I311" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J311" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K311" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="312" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12555,34 +12718,34 @@
         <v>227</v>
       </c>
       <c r="B312" s="3">
-        <v>883</v>
+        <v>275</v>
       </c>
       <c r="C312" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D312" s="2">
         <v>1</v>
       </c>
       <c r="E312" s="2">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F312" s="4">
         <f>B312/E312</f>
       </c>
       <c r="G312" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I312" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K312" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="313" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12590,22 +12753,22 @@
         <v>227</v>
       </c>
       <c r="B313" s="3">
-        <v>636</v>
+        <v>990</v>
       </c>
       <c r="C313" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D313" s="2">
         <v>1</v>
       </c>
       <c r="E313" s="2">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F313" s="4">
         <f>B313/E313</f>
       </c>
       <c r="G313" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>13</v>
@@ -12614,10 +12777,10 @@
         <v>13</v>
       </c>
       <c r="J313" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K313" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="314" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12625,25 +12788,25 @@
         <v>227</v>
       </c>
       <c r="B314" s="3">
-        <v>259</v>
+        <v>490</v>
       </c>
       <c r="C314" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D314" s="2">
         <v>1</v>
       </c>
       <c r="E314" s="2">
-        <v>43.6</v>
+        <v>63</v>
       </c>
       <c r="F314" s="4">
         <f>B314/E314</f>
       </c>
       <c r="G314" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I314" s="2" t="s">
         <v>16</v>
@@ -12652,7 +12815,7 @@
         <v>13</v>
       </c>
       <c r="K314" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="315" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12660,10 +12823,10 @@
         <v>227</v>
       </c>
       <c r="B315" s="3">
-        <v>700</v>
+        <v>426</v>
       </c>
       <c r="C315" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D315" s="2">
         <v>1</v>
@@ -12675,7 +12838,7 @@
         <f>B315/E315</f>
       </c>
       <c r="G315" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>13</v>
@@ -12684,10 +12847,10 @@
         <v>13</v>
       </c>
       <c r="J315" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K315" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="316" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12695,34 +12858,34 @@
         <v>227</v>
       </c>
       <c r="B316" s="3">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="C316" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D316" s="2">
         <v>1</v>
       </c>
       <c r="E316" s="2">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="F316" s="4">
         <f>B316/E316</f>
       </c>
       <c r="G316" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I316" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J316" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K316" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="317" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12730,7 +12893,7 @@
         <v>227</v>
       </c>
       <c r="B317" s="3">
-        <v>227</v>
+        <v>570</v>
       </c>
       <c r="C317" s="2">
         <v>3</v>
@@ -12739,13 +12902,13 @@
         <v>1</v>
       </c>
       <c r="E317" s="2">
-        <v>60.8</v>
+        <v>64</v>
       </c>
       <c r="F317" s="4">
         <f>B317/E317</f>
       </c>
       <c r="G317" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>13</v>
@@ -12757,7 +12920,7 @@
         <v>16</v>
       </c>
       <c r="K317" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="318" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12765,34 +12928,34 @@
         <v>227</v>
       </c>
       <c r="B318" s="3">
-        <v>520</v>
+        <v>100</v>
       </c>
       <c r="C318" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D318" s="2">
         <v>1</v>
       </c>
       <c r="E318" s="2">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="F318" s="4">
         <f>B318/E318</f>
       </c>
       <c r="G318" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I318" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K318" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="319" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12800,7 +12963,7 @@
         <v>227</v>
       </c>
       <c r="B319" s="3">
-        <v>515</v>
+        <v>700</v>
       </c>
       <c r="C319" s="2">
         <v>3</v>
@@ -12809,25 +12972,25 @@
         <v>1</v>
       </c>
       <c r="E319" s="2">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F319" s="4">
         <f>B319/E319</f>
       </c>
       <c r="G319" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I319" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K319" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="320" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12835,34 +12998,34 @@
         <v>227</v>
       </c>
       <c r="B320" s="3">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="C320" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D320" s="2">
         <v>1</v>
       </c>
       <c r="E320" s="2">
-        <v>48.4</v>
+        <v>79</v>
       </c>
       <c r="F320" s="4">
         <f>B320/E320</f>
       </c>
       <c r="G320" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I320" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J320" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K320" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="321" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12870,22 +13033,22 @@
         <v>227</v>
       </c>
       <c r="B321" s="3">
-        <v>947</v>
+        <v>490</v>
       </c>
       <c r="C321" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D321" s="2">
         <v>1</v>
       </c>
       <c r="E321" s="2">
-        <v>79.5</v>
+        <v>50</v>
       </c>
       <c r="F321" s="4">
         <f>B321/E321</f>
       </c>
       <c r="G321" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>13</v>
@@ -12894,10 +13057,10 @@
         <v>13</v>
       </c>
       <c r="J321" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K321" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="322" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12905,25 +13068,25 @@
         <v>227</v>
       </c>
       <c r="B322" s="3">
-        <v>990</v>
+        <v>800</v>
       </c>
       <c r="C322" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D322" s="2">
         <v>1</v>
       </c>
       <c r="E322" s="2">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="F322" s="4">
         <f>B322/E322</f>
       </c>
       <c r="G322" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I322" s="2" t="s">
         <v>16</v>
@@ -12932,7 +13095,7 @@
         <v>13</v>
       </c>
       <c r="K322" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="323" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12940,7 +13103,7 @@
         <v>227</v>
       </c>
       <c r="B323" s="3">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C323" s="2">
         <v>3</v>
@@ -12949,25 +13112,25 @@
         <v>1</v>
       </c>
       <c r="E323" s="2">
-        <v>65.7</v>
+        <v>64</v>
       </c>
       <c r="F323" s="4">
         <f>B323/E323</f>
       </c>
       <c r="G323" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I323" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K323" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="324" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12975,34 +13138,34 @@
         <v>227</v>
       </c>
       <c r="B324" s="3">
-        <v>483</v>
+        <v>261</v>
       </c>
       <c r="C324" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D324" s="2">
         <v>1</v>
       </c>
       <c r="E324" s="2">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F324" s="4">
         <f>B324/E324</f>
       </c>
       <c r="G324" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I324" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J324" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K324" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="325" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13010,22 +13173,22 @@
         <v>227</v>
       </c>
       <c r="B325" s="3">
-        <v>194</v>
+        <v>38</v>
       </c>
       <c r="C325" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D325" s="2">
         <v>1</v>
       </c>
       <c r="E325" s="2">
-        <v>33.5</v>
+        <v>81</v>
       </c>
       <c r="F325" s="4">
         <f>B325/E325</f>
       </c>
       <c r="G325" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>13</v>
@@ -13034,10 +13197,10 @@
         <v>16</v>
       </c>
       <c r="J325" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K325" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="326" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13045,34 +13208,32 @@
         <v>227</v>
       </c>
       <c r="B326" s="3">
-        <v>346</v>
+        <v>620</v>
       </c>
       <c r="C326" s="2">
-        <v>3</v>
-      </c>
-      <c r="D326" s="2">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D326" s="2"/>
       <c r="E326" s="2">
-        <v>71</v>
+        <v>9.9</v>
       </c>
       <c r="F326" s="4">
         <f>B326/E326</f>
       </c>
       <c r="G326" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I326" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J326" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K326" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="327" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13080,32 +13241,34 @@
         <v>227</v>
       </c>
       <c r="B327" s="3">
-        <v>490</v>
+        <v>967</v>
       </c>
       <c r="C327" s="2">
-        <v>1</v>
-      </c>
-      <c r="D327" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="D327" s="2">
+        <v>1</v>
+      </c>
       <c r="E327" s="2">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F327" s="4">
         <f>B327/E327</f>
       </c>
       <c r="G327" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I327" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J327" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K327" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="328" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13113,25 +13276,25 @@
         <v>227</v>
       </c>
       <c r="B328" s="3">
-        <v>387</v>
+        <v>590</v>
       </c>
       <c r="C328" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D328" s="2">
         <v>1</v>
       </c>
       <c r="E328" s="2">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="F328" s="4">
         <f>B328/E328</f>
       </c>
       <c r="G328" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I328" s="2" t="s">
         <v>13</v>
@@ -13140,7 +13303,7 @@
         <v>13</v>
       </c>
       <c r="K328" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="329" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13148,7 +13311,7 @@
         <v>227</v>
       </c>
       <c r="B329" s="3">
-        <v>371</v>
+        <v>935</v>
       </c>
       <c r="C329" s="2">
         <v>2</v>
@@ -13157,25 +13320,25 @@
         <v>1</v>
       </c>
       <c r="E329" s="2">
-        <v>47.3</v>
+        <v>34</v>
       </c>
       <c r="F329" s="4">
         <f>B329/E329</f>
       </c>
       <c r="G329" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I329" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J329" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K329" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="330" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13183,25 +13346,25 @@
         <v>227</v>
       </c>
       <c r="B330" s="3">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="C330" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D330" s="2">
         <v>1</v>
       </c>
       <c r="E330" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F330" s="4">
         <f>B330/E330</f>
       </c>
       <c r="G330" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I330" s="2" t="s">
         <v>13</v>
@@ -13210,7 +13373,7 @@
         <v>13</v>
       </c>
       <c r="K330" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="331" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13218,34 +13381,34 @@
         <v>227</v>
       </c>
       <c r="B331" s="3">
-        <v>220</v>
+        <v>890</v>
       </c>
       <c r="C331" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D331" s="2">
         <v>1</v>
       </c>
       <c r="E331" s="2">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="F331" s="4">
         <f>B331/E331</f>
       </c>
       <c r="G331" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I331" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J331" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K331" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="332" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13253,22 +13416,22 @@
         <v>227</v>
       </c>
       <c r="B332" s="3">
-        <v>194</v>
+        <v>600</v>
       </c>
       <c r="C332" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D332" s="2">
         <v>1</v>
       </c>
       <c r="E332" s="2">
-        <v>33.5</v>
+        <v>116</v>
       </c>
       <c r="F332" s="4">
         <f>B332/E332</f>
       </c>
       <c r="G332" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>13</v>
@@ -13280,7 +13443,7 @@
         <v>16</v>
       </c>
       <c r="K332" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="333" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13288,34 +13451,34 @@
         <v>227</v>
       </c>
       <c r="B333" s="3">
-        <v>378</v>
+        <v>253</v>
       </c>
       <c r="C333" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D333" s="2">
         <v>1</v>
       </c>
       <c r="E333" s="2">
-        <v>41</v>
+        <v>50.4</v>
       </c>
       <c r="F333" s="4">
         <f>B333/E333</f>
       </c>
       <c r="G333" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H333" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I333" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J333" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K333" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="334" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13323,22 +13486,22 @@
         <v>227</v>
       </c>
       <c r="B334" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="C334" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D334" s="2">
         <v>1</v>
       </c>
       <c r="E334" s="2">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="F334" s="4">
         <f>B334/E334</f>
       </c>
       <c r="G334" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>13</v>
@@ -13347,10 +13510,10 @@
         <v>13</v>
       </c>
       <c r="J334" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K334" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="335" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13358,34 +13521,1858 @@
         <v>227</v>
       </c>
       <c r="B335" s="3">
-        <v>320</v>
+        <v>795</v>
       </c>
       <c r="C335" s="2">
-        <v>5</v>
-      </c>
-      <c r="D335" s="2">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D335" s="2"/>
       <c r="E335" s="2">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="F335" s="4">
         <f>B335/E335</f>
       </c>
       <c r="G335" s="2" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="H335" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I335" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J335" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K335" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B336" s="3">
+        <v>25</v>
+      </c>
+      <c r="C336" s="2">
+        <v>2</v>
+      </c>
+      <c r="D336" s="2">
+        <v>1</v>
+      </c>
+      <c r="E336" s="2">
+        <v>45</v>
+      </c>
+      <c r="F336" s="4">
+        <f>B336/E336</f>
+      </c>
+      <c r="G336" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H336" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I336" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J336" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K336" s="2" t="s">
         <v>429</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A337" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B337" s="3">
+        <v>526</v>
+      </c>
+      <c r="C337" s="2">
+        <v>2</v>
+      </c>
+      <c r="D337" s="2">
+        <v>1</v>
+      </c>
+      <c r="E337" s="2">
+        <v>50.1</v>
+      </c>
+      <c r="F337" s="4">
+        <f>B337/E337</f>
+      </c>
+      <c r="G337" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H337" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I337" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J337" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K337" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A338" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B338" s="3">
+        <v>404</v>
+      </c>
+      <c r="C338" s="2">
+        <v>2</v>
+      </c>
+      <c r="D338" s="2"/>
+      <c r="E338" s="2">
+        <v>53.6</v>
+      </c>
+      <c r="F338" s="4">
+        <f>B338/E338</f>
+      </c>
+      <c r="G338" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H338" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I338" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J338" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K338" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A339" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B339" s="3">
+        <v>200</v>
+      </c>
+      <c r="C339" s="2">
+        <v>3</v>
+      </c>
+      <c r="D339" s="2">
+        <v>1</v>
+      </c>
+      <c r="E339" s="2">
+        <v>48</v>
+      </c>
+      <c r="F339" s="4">
+        <f>B339/E339</f>
+      </c>
+      <c r="G339" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H339" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I339" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J339" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K339" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B340" s="3">
+        <v>0</v>
+      </c>
+      <c r="C340" s="2">
+        <v>3</v>
+      </c>
+      <c r="D340" s="2">
+        <v>1</v>
+      </c>
+      <c r="E340" s="2">
+        <v>57</v>
+      </c>
+      <c r="G340" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H340" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I340" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J340" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K340" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B341" s="3">
+        <v>350</v>
+      </c>
+      <c r="C341" s="2">
+        <v>3</v>
+      </c>
+      <c r="D341" s="2">
+        <v>1</v>
+      </c>
+      <c r="E341" s="2">
+        <v>77</v>
+      </c>
+      <c r="F341" s="4">
+        <f>B341/E341</f>
+      </c>
+      <c r="G341" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H341" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I341" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J341" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K341" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A342" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B342" s="3">
+        <v>375</v>
+      </c>
+      <c r="C342" s="2">
+        <v>4</v>
+      </c>
+      <c r="D342" s="2">
+        <v>1</v>
+      </c>
+      <c r="E342" s="2">
+        <v>87</v>
+      </c>
+      <c r="F342" s="4">
+        <f>B342/E342</f>
+      </c>
+      <c r="G342" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H342" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I342" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J342" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K342" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A343" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B343" s="3">
+        <v>883</v>
+      </c>
+      <c r="C343" s="2">
+        <v>1</v>
+      </c>
+      <c r="D343" s="2">
+        <v>1</v>
+      </c>
+      <c r="E343" s="2">
+        <v>21</v>
+      </c>
+      <c r="F343" s="4">
+        <f>B343/E343</f>
+      </c>
+      <c r="G343" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H343" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I343" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J343" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K343" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A344" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B344" s="3">
+        <v>636</v>
+      </c>
+      <c r="C344" s="2">
+        <v>5</v>
+      </c>
+      <c r="D344" s="2">
+        <v>1</v>
+      </c>
+      <c r="E344" s="2">
+        <v>102</v>
+      </c>
+      <c r="F344" s="4">
+        <f>B344/E344</f>
+      </c>
+      <c r="G344" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H344" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I344" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J344" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K344" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A345" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B345" s="3">
+        <v>259</v>
+      </c>
+      <c r="C345" s="2">
+        <v>2</v>
+      </c>
+      <c r="D345" s="2">
+        <v>1</v>
+      </c>
+      <c r="E345" s="2">
+        <v>43.6</v>
+      </c>
+      <c r="F345" s="4">
+        <f>B345/E345</f>
+      </c>
+      <c r="G345" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H345" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I345" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J345" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K345" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A346" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B346" s="3">
+        <v>700</v>
+      </c>
+      <c r="C346" s="2">
+        <v>3</v>
+      </c>
+      <c r="D346" s="2">
+        <v>1</v>
+      </c>
+      <c r="E346" s="2">
+        <v>53</v>
+      </c>
+      <c r="F346" s="4">
+        <f>B346/E346</f>
+      </c>
+      <c r="G346" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H346" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I346" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J346" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K346" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A347" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B347" s="3">
+        <v>550</v>
+      </c>
+      <c r="C347" s="2">
+        <v>3</v>
+      </c>
+      <c r="D347" s="2">
+        <v>1</v>
+      </c>
+      <c r="E347" s="2">
+        <v>62</v>
+      </c>
+      <c r="F347" s="4">
+        <f>B347/E347</f>
+      </c>
+      <c r="G347" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H347" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I347" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J347" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K347" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A348" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B348" s="3">
+        <v>227</v>
+      </c>
+      <c r="C348" s="2">
+        <v>3</v>
+      </c>
+      <c r="D348" s="2">
+        <v>1</v>
+      </c>
+      <c r="E348" s="2">
+        <v>60.8</v>
+      </c>
+      <c r="F348" s="4">
+        <f>B348/E348</f>
+      </c>
+      <c r="G348" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H348" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I348" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J348" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K348" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A349" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B349" s="3">
+        <v>520</v>
+      </c>
+      <c r="C349" s="2">
+        <v>1</v>
+      </c>
+      <c r="D349" s="2">
+        <v>1</v>
+      </c>
+      <c r="E349" s="2">
+        <v>9</v>
+      </c>
+      <c r="F349" s="4">
+        <f>B349/E349</f>
+      </c>
+      <c r="G349" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H349" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I349" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J349" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K349" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A350" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B350" s="3">
+        <v>515</v>
+      </c>
+      <c r="C350" s="2">
+        <v>3</v>
+      </c>
+      <c r="D350" s="2">
+        <v>1</v>
+      </c>
+      <c r="E350" s="2">
+        <v>63</v>
+      </c>
+      <c r="F350" s="4">
+        <f>B350/E350</f>
+      </c>
+      <c r="G350" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H350" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I350" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J350" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K350" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="351" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A351" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B351" s="3">
+        <v>141</v>
+      </c>
+      <c r="C351" s="2">
+        <v>2</v>
+      </c>
+      <c r="D351" s="2">
+        <v>1</v>
+      </c>
+      <c r="E351" s="2">
+        <v>48.4</v>
+      </c>
+      <c r="F351" s="4">
+        <f>B351/E351</f>
+      </c>
+      <c r="G351" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H351" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I351" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J351" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K351" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="352" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A352" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B352" s="3">
+        <v>947</v>
+      </c>
+      <c r="C352" s="2">
+        <v>4</v>
+      </c>
+      <c r="D352" s="2">
+        <v>1</v>
+      </c>
+      <c r="E352" s="2">
+        <v>79.5</v>
+      </c>
+      <c r="F352" s="4">
+        <f>B352/E352</f>
+      </c>
+      <c r="G352" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H352" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I352" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J352" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K352" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="353" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A353" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B353" s="3">
+        <v>990</v>
+      </c>
+      <c r="C353" s="2">
+        <v>2</v>
+      </c>
+      <c r="D353" s="2">
+        <v>1</v>
+      </c>
+      <c r="E353" s="2">
+        <v>30</v>
+      </c>
+      <c r="F353" s="4">
+        <f>B353/E353</f>
+      </c>
+      <c r="G353" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H353" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I353" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J353" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K353" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="354" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B354" s="3">
+        <v>579</v>
+      </c>
+      <c r="C354" s="2">
+        <v>3</v>
+      </c>
+      <c r="D354" s="2">
+        <v>1</v>
+      </c>
+      <c r="E354" s="2">
+        <v>65.7</v>
+      </c>
+      <c r="F354" s="4">
+        <f>B354/E354</f>
+      </c>
+      <c r="G354" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H354" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I354" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J354" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K354" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="355" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A355" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B355" s="3">
+        <v>483</v>
+      </c>
+      <c r="C355" s="2">
+        <v>2</v>
+      </c>
+      <c r="D355" s="2">
+        <v>1</v>
+      </c>
+      <c r="E355" s="2">
+        <v>66</v>
+      </c>
+      <c r="F355" s="4">
+        <f>B355/E355</f>
+      </c>
+      <c r="G355" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H355" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I355" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J355" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K355" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="356" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B356" s="3">
+        <v>194</v>
+      </c>
+      <c r="C356" s="2">
+        <v>2</v>
+      </c>
+      <c r="D356" s="2">
+        <v>1</v>
+      </c>
+      <c r="E356" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="F356" s="4">
+        <f>B356/E356</f>
+      </c>
+      <c r="G356" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H356" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I356" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J356" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K356" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="357" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A357" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B357" s="3">
+        <v>346</v>
+      </c>
+      <c r="C357" s="2">
+        <v>3</v>
+      </c>
+      <c r="D357" s="2">
+        <v>1</v>
+      </c>
+      <c r="E357" s="2">
+        <v>71</v>
+      </c>
+      <c r="F357" s="4">
+        <f>B357/E357</f>
+      </c>
+      <c r="G357" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H357" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I357" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J357" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K357" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="358" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B358" s="3">
+        <v>490</v>
+      </c>
+      <c r="C358" s="2">
+        <v>1</v>
+      </c>
+      <c r="D358" s="2"/>
+      <c r="E358" s="2">
+        <v>14</v>
+      </c>
+      <c r="F358" s="4">
+        <f>B358/E358</f>
+      </c>
+      <c r="G358" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H358" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I358" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J358" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K358" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="359" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A359" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B359" s="3">
+        <v>387</v>
+      </c>
+      <c r="C359" s="2">
+        <v>1</v>
+      </c>
+      <c r="D359" s="2">
+        <v>1</v>
+      </c>
+      <c r="E359" s="2">
+        <v>40</v>
+      </c>
+      <c r="F359" s="4">
+        <f>B359/E359</f>
+      </c>
+      <c r="G359" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H359" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I359" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J359" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K359" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="360" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B360" s="3">
+        <v>371</v>
+      </c>
+      <c r="C360" s="2">
+        <v>2</v>
+      </c>
+      <c r="D360" s="2">
+        <v>1</v>
+      </c>
+      <c r="E360" s="2">
+        <v>47.3</v>
+      </c>
+      <c r="F360" s="4">
+        <f>B360/E360</f>
+      </c>
+      <c r="G360" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H360" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I360" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J360" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K360" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="361" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A361" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B361" s="3">
+        <v>650</v>
+      </c>
+      <c r="C361" s="2">
+        <v>3</v>
+      </c>
+      <c r="D361" s="2">
+        <v>1</v>
+      </c>
+      <c r="E361" s="2">
+        <v>72</v>
+      </c>
+      <c r="F361" s="4">
+        <f>B361/E361</f>
+      </c>
+      <c r="G361" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H361" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I361" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J361" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K361" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="362" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B362" s="3">
+        <v>220</v>
+      </c>
+      <c r="C362" s="2">
+        <v>2</v>
+      </c>
+      <c r="D362" s="2">
+        <v>1</v>
+      </c>
+      <c r="E362" s="2">
+        <v>31</v>
+      </c>
+      <c r="F362" s="4">
+        <f>B362/E362</f>
+      </c>
+      <c r="G362" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H362" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I362" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J362" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K362" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="363" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A363" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B363" s="3">
+        <v>194</v>
+      </c>
+      <c r="C363" s="2">
+        <v>2</v>
+      </c>
+      <c r="D363" s="2">
+        <v>1</v>
+      </c>
+      <c r="E363" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="F363" s="4">
+        <f>B363/E363</f>
+      </c>
+      <c r="G363" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H363" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I363" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J363" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K363" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="364" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B364" s="3">
+        <v>378</v>
+      </c>
+      <c r="C364" s="2">
+        <v>2</v>
+      </c>
+      <c r="D364" s="2">
+        <v>1</v>
+      </c>
+      <c r="E364" s="2">
+        <v>41</v>
+      </c>
+      <c r="F364" s="4">
+        <f>B364/E364</f>
+      </c>
+      <c r="G364" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H364" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I364" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J364" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K364" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="365" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B365" s="3">
+        <v>800</v>
+      </c>
+      <c r="C365" s="2">
+        <v>5</v>
+      </c>
+      <c r="D365" s="2">
+        <v>1</v>
+      </c>
+      <c r="E365" s="2">
+        <v>98</v>
+      </c>
+      <c r="F365" s="4">
+        <f>B365/E365</f>
+      </c>
+      <c r="G365" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H365" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I365" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J365" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K365" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="366" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A366" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B366" s="3">
+        <v>320</v>
+      </c>
+      <c r="C366" s="2">
+        <v>5</v>
+      </c>
+      <c r="D366" s="2">
+        <v>1</v>
+      </c>
+      <c r="E366" s="2">
+        <v>110</v>
+      </c>
+      <c r="F366" s="4">
+        <f>B366/E366</f>
+      </c>
+      <c r="G366" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H366" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I366" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J366" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K366" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="367" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A367" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B367" s="3">
+        <v>850</v>
+      </c>
+      <c r="C367" s="2">
+        <v>2</v>
+      </c>
+      <c r="D367" s="2">
+        <v>1</v>
+      </c>
+      <c r="E367" s="2">
+        <v>60</v>
+      </c>
+      <c r="F367" s="4">
+        <f>B367/E367</f>
+      </c>
+      <c r="G367" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H367" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I367" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J367" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K367" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A368" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B368" s="3">
+        <v>384</v>
+      </c>
+      <c r="C368" s="2">
+        <v>1</v>
+      </c>
+      <c r="D368" s="2"/>
+      <c r="E368" s="2">
+        <v>18</v>
+      </c>
+      <c r="F368" s="4">
+        <f>B368/E368</f>
+      </c>
+      <c r="G368" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H368" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I368" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J368" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K368" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A369" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B369" s="3">
+        <v>454</v>
+      </c>
+      <c r="C369" s="2">
+        <v>1</v>
+      </c>
+      <c r="D369" s="2"/>
+      <c r="E369" s="2">
+        <v>62</v>
+      </c>
+      <c r="F369" s="4">
+        <f>B369/E369</f>
+      </c>
+      <c r="G369" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H369" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I369" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J369" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K369" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A370" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B370" s="3">
+        <v>891</v>
+      </c>
+      <c r="C370" s="2">
+        <v>1</v>
+      </c>
+      <c r="D370" s="2"/>
+      <c r="E370" s="2">
+        <v>30</v>
+      </c>
+      <c r="F370" s="4">
+        <f>B370/E370</f>
+      </c>
+      <c r="G370" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H370" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I370" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J370" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K370" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A371" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B371" s="3">
+        <v>946</v>
+      </c>
+      <c r="C371" s="2">
+        <v>1</v>
+      </c>
+      <c r="D371" s="2"/>
+      <c r="E371" s="2">
+        <v>38</v>
+      </c>
+      <c r="F371" s="4">
+        <f>B371/E371</f>
+      </c>
+      <c r="G371" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H371" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I371" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J371" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K371" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="372" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B372" s="3">
+        <v>472</v>
+      </c>
+      <c r="C372" s="2">
+        <v>1</v>
+      </c>
+      <c r="D372" s="2"/>
+      <c r="E372" s="2">
+        <v>32</v>
+      </c>
+      <c r="F372" s="4">
+        <f>B372/E372</f>
+      </c>
+      <c r="G372" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H372" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I372" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J372" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K372" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="373" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A373" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B373" s="3">
+        <v>860</v>
+      </c>
+      <c r="C373" s="2">
+        <v>2</v>
+      </c>
+      <c r="D373" s="2">
+        <v>1</v>
+      </c>
+      <c r="E373" s="2">
+        <v>54</v>
+      </c>
+      <c r="F373" s="4">
+        <f>B373/E373</f>
+      </c>
+      <c r="G373" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H373" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I373" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J373" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K373" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A374" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B374" s="3">
+        <v>32</v>
+      </c>
+      <c r="C374" s="2">
+        <v>3</v>
+      </c>
+      <c r="D374" s="2">
+        <v>2</v>
+      </c>
+      <c r="E374" s="2">
+        <v>58</v>
+      </c>
+      <c r="F374" s="4">
+        <f>B374/E374</f>
+      </c>
+      <c r="G374" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H374" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I374" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J374" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K374" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A375" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B375" s="3">
+        <v>300</v>
+      </c>
+      <c r="C375" s="2">
+        <v>2</v>
+      </c>
+      <c r="D375" s="2">
+        <v>1</v>
+      </c>
+      <c r="E375" s="2">
+        <v>55</v>
+      </c>
+      <c r="F375" s="4">
+        <f>B375/E375</f>
+      </c>
+      <c r="G375" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H375" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I375" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J375" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K375" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A376" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B376" s="3">
+        <v>620</v>
+      </c>
+      <c r="C376" s="2">
+        <v>3</v>
+      </c>
+      <c r="D376" s="2">
+        <v>2</v>
+      </c>
+      <c r="E376" s="2">
+        <v>91</v>
+      </c>
+      <c r="F376" s="4">
+        <f>B376/E376</f>
+      </c>
+      <c r="G376" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H376" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I376" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J376" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K376" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="377" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B377" s="3">
+        <v>545</v>
+      </c>
+      <c r="C377" s="2">
+        <v>1</v>
+      </c>
+      <c r="D377" s="2"/>
+      <c r="E377" s="2">
+        <v>25</v>
+      </c>
+      <c r="F377" s="4">
+        <f>B377/E377</f>
+      </c>
+      <c r="G377" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H377" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I377" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J377" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K377" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A378" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B378" s="3">
+        <v>0</v>
+      </c>
+      <c r="C378" s="2">
+        <v>4</v>
+      </c>
+      <c r="D378" s="2"/>
+      <c r="E378" s="2">
+        <v>80</v>
+      </c>
+      <c r="G378" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H378" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I378" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J378" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K378" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="379" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A379" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B379" s="3">
+        <v>200</v>
+      </c>
+      <c r="C379" s="2">
+        <v>8</v>
+      </c>
+      <c r="D379" s="2">
+        <v>5</v>
+      </c>
+      <c r="E379" s="2">
+        <v>175</v>
+      </c>
+      <c r="F379" s="4">
+        <f>B379/E379</f>
+      </c>
+      <c r="G379" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H379" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I379" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J379" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K379" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="380" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A380" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B380" s="3">
+        <v>10</v>
+      </c>
+      <c r="C380" s="2">
+        <v>2</v>
+      </c>
+      <c r="D380" s="2">
+        <v>2</v>
+      </c>
+      <c r="E380" s="2">
+        <v>50</v>
+      </c>
+      <c r="F380" s="4">
+        <f>B380/E380</f>
+      </c>
+      <c r="G380" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H380" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I380" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J380" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K380" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A381" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B381" s="3">
+        <v>915</v>
+      </c>
+      <c r="C381" s="2">
+        <v>2</v>
+      </c>
+      <c r="D381" s="2">
+        <v>1</v>
+      </c>
+      <c r="E381" s="2">
+        <v>38.9</v>
+      </c>
+      <c r="F381" s="4">
+        <f>B381/E381</f>
+      </c>
+      <c r="G381" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H381" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I381" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J381" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K381" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A382" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B382" s="3">
+        <v>690</v>
+      </c>
+      <c r="C382" s="2">
+        <v>1</v>
+      </c>
+      <c r="D382" s="2">
+        <v>1</v>
+      </c>
+      <c r="E382" s="2">
+        <v>31</v>
+      </c>
+      <c r="F382" s="4">
+        <f>B382/E382</f>
+      </c>
+      <c r="G382" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H382" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I382" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J382" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K382" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="383" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A383" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B383" s="3">
+        <v>440</v>
+      </c>
+      <c r="C383" s="2">
+        <v>5</v>
+      </c>
+      <c r="D383" s="2">
+        <v>2</v>
+      </c>
+      <c r="E383" s="2">
+        <v>110</v>
+      </c>
+      <c r="F383" s="4">
+        <f>B383/E383</f>
+      </c>
+      <c r="G383" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H383" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I383" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J383" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K383" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A384" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B384" s="3">
+        <v>100</v>
+      </c>
+      <c r="C384" s="2">
+        <v>1</v>
+      </c>
+      <c r="D384" s="2">
+        <v>1</v>
+      </c>
+      <c r="E384" s="2">
+        <v>36.4</v>
+      </c>
+      <c r="F384" s="4">
+        <f>B384/E384</f>
+      </c>
+      <c r="G384" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H384" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I384" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J384" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K384" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B385" s="3">
+        <v>363</v>
+      </c>
+      <c r="C385" s="2">
+        <v>2</v>
+      </c>
+      <c r="D385" s="2">
+        <v>1</v>
+      </c>
+      <c r="E385" s="2">
+        <v>30</v>
+      </c>
+      <c r="F385" s="4">
+        <f>B385/E385</f>
+      </c>
+      <c r="G385" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H385" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I385" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J385" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K385" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A386" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B386" s="3">
+        <v>950</v>
+      </c>
+      <c r="C386" s="2">
+        <v>3</v>
+      </c>
+      <c r="D386" s="2">
+        <v>1</v>
+      </c>
+      <c r="E386" s="2">
+        <v>89</v>
+      </c>
+      <c r="F386" s="4">
+        <f>B386/E386</f>
+      </c>
+      <c r="G386" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H386" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I386" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J386" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K386" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A387" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B387" s="3">
+        <v>17</v>
+      </c>
+      <c r="C387" s="2">
+        <v>1</v>
+      </c>
+      <c r="D387" s="2">
+        <v>1</v>
+      </c>
+      <c r="E387" s="2"/>
+      <c r="G387" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H387" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I387" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J387" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K387" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="388" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A388" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B388" s="3">
+        <v>726</v>
+      </c>
+      <c r="C388" s="2">
+        <v>5</v>
+      </c>
+      <c r="D388" s="2">
+        <v>1</v>
+      </c>
+      <c r="E388" s="2">
+        <v>143</v>
+      </c>
+      <c r="F388" s="4">
+        <f>B388/E388</f>
+      </c>
+      <c r="G388" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H388" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I388" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J388" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K388" s="2" t="s">
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -13397,7 +15384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
@@ -13405,212 +15392,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>430</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>431</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>432</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>433</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>434</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>435</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>436</v>
+      <c r="A7" s="6" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>437</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>438</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>439</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>441</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>442</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>443</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>444</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>445</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>446</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>447</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>448</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>449</v>
+        <v>502</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>450</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>451</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>452</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>453</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>454</v>
+        <v>507</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>456</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>457</v>
+        <v>510</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>458</v>
+        <v>511</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>459</v>
+        <v>512</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>460</v>
+        <v>513</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>461</v>
+        <v>514</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>462</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>463</v>
+        <v>516</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>464</v>
+        <v>517</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>465</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>466</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>467</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>468</v>
+        <v>521</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>469</v>
+        <v>522</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>471</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
